--- a/STT Report Elite Marketing (20-06-26) (1).xlsx
+++ b/STT Report Elite Marketing (20-06-26) (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F75FD68-2E5C-4DD7-B2A9-74F10B4972ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9492B1B7-E0D6-4BBB-A0C4-549B829E686C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="490">
   <si>
     <t>Date</t>
   </si>
@@ -1293,6 +1293,213 @@
   <si>
     <t>Nadra Abad</t>
   </si>
+  <si>
+    <t>Chaudry Road</t>
+  </si>
+  <si>
+    <t>Lawrance Road</t>
+  </si>
+  <si>
+    <t>Sohna Dipartmental Store</t>
+  </si>
+  <si>
+    <t>Mason Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghosia Bakers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Fazal Cash &amp; Carry </t>
+  </si>
+  <si>
+    <t>Nishat Colony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Ahmad Sweets </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS Sweet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A one Baker </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nishter </t>
+  </si>
+  <si>
+    <t>Nishter Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalasha Bakery </t>
+  </si>
+  <si>
+    <t>Salman Store</t>
+  </si>
+  <si>
+    <t>Bhola Store</t>
+  </si>
+  <si>
+    <t>Bismillah Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shareef Mart </t>
+  </si>
+  <si>
+    <t>Latif Store</t>
+  </si>
+  <si>
+    <t>Bakhtawar Store</t>
+  </si>
+  <si>
+    <t>Honey Store</t>
+  </si>
+  <si>
+    <t>Walton Road</t>
+  </si>
+  <si>
+    <t>Askari Walfair Store</t>
+  </si>
+  <si>
+    <t>Tajbhag phase 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhatti Mart </t>
+  </si>
+  <si>
+    <t>Sooter mill</t>
+  </si>
+  <si>
+    <t>Umer</t>
+  </si>
+  <si>
+    <t>Haseeb Store</t>
+  </si>
+  <si>
+    <t>Asiq Store</t>
+  </si>
+  <si>
+    <t>Gulberg 3</t>
+  </si>
+  <si>
+    <t>Al Madina Photo copy</t>
+  </si>
+  <si>
+    <t>Chishtiyan Sabrian Store</t>
+  </si>
+  <si>
+    <t>Aashiyana Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Street </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamza Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abu Hunain </t>
+  </si>
+  <si>
+    <t>Youna Abad</t>
+  </si>
+  <si>
+    <t>bibi Store</t>
+  </si>
+  <si>
+    <t>Grocer Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Mart </t>
+  </si>
+  <si>
+    <t>Cv Store</t>
+  </si>
+  <si>
+    <t>Afzal Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajwa Bakers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Mart </t>
+  </si>
+  <si>
+    <t>Shop no 4</t>
+  </si>
+  <si>
+    <t>Younas Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Captain Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sui Gas Society </t>
+  </si>
+  <si>
+    <t>Badami Bagh</t>
+  </si>
+  <si>
+    <t>Begum Kot</t>
+  </si>
+  <si>
+    <t>Imamia Colony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilal Ganj </t>
+  </si>
+  <si>
+    <t>Islam Pura</t>
+  </si>
+  <si>
+    <t>Kareem Park</t>
+  </si>
+  <si>
+    <t>Kot Abdul malik</t>
+  </si>
+  <si>
+    <t>Krishan Nager</t>
+  </si>
+  <si>
+    <t>Lakshman</t>
+  </si>
+  <si>
+    <t>Shadra</t>
+  </si>
+  <si>
+    <t>Sana Cash &amp; Carry</t>
+  </si>
+  <si>
+    <t>Gourmet Food DHA Rahber</t>
+  </si>
+  <si>
+    <t>Gourmet Food Bahria Town</t>
+  </si>
+  <si>
+    <t>Jalal Sons Bahria Orchard</t>
+  </si>
+  <si>
+    <t>Shehwar Mega Mart</t>
+  </si>
+  <si>
+    <t>Rainbow BT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wapda Town </t>
+  </si>
+  <si>
+    <t>DHA Rehber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baria Town </t>
+  </si>
+  <si>
+    <t>Bahria Orchard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jublee Town </t>
+  </si>
+  <si>
+    <t>Bahria Town</t>
+  </si>
 </sst>
 </file>
 
@@ -1911,7 +2118,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2183,22 +2390,25 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2210,11 +2420,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2233,10 +2443,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2604,22 +2810,22 @@
       <c r="B1" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="106" t="s">
+      <c r="C1" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="106" t="s">
+      <c r="F1" s="102" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="106" t="s">
+      <c r="H1" s="102" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
@@ -2630,82 +2836,82 @@
       <c r="L1" s="105"/>
       <c r="M1" s="105"/>
       <c r="N1" s="105"/>
-      <c r="O1" s="110" t="s">
+      <c r="O1" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="107" t="s">
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="109" t="s">
+      <c r="T1" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109" t="s">
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="103" t="s">
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="103" t="s">
+      <c r="AC1" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="103" t="s">
+      <c r="AD1" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="103" t="s">
+      <c r="AE1" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="103" t="s">
+      <c r="AF1" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="103" t="s">
+      <c r="AG1" s="106" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="103" t="s">
+      <c r="AI1" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="103" t="s">
+      <c r="AJ1" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="103" t="s">
+      <c r="AK1" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="103" t="s">
+      <c r="AL1" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="103" t="s">
+      <c r="AM1" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="101" t="s">
+      <c r="AN1" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="101" t="s">
+      <c r="AO1" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="103" t="s">
+      <c r="AP1" s="106" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="105"/>
       <c r="B2" s="105"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
       <c r="G2" s="105"/>
-      <c r="H2" s="106"/>
+      <c r="H2" s="102"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -2736,7 +2942,7 @@
       <c r="R2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="108"/>
+      <c r="S2" s="109"/>
       <c r="T2" s="4" t="s">
         <v>353</v>
       </c>
@@ -2761,23 +2967,23 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="104"/>
-      <c r="AC2" s="104"/>
-      <c r="AD2" s="104"/>
-      <c r="AE2" s="104"/>
-      <c r="AF2" s="104"/>
-      <c r="AG2" s="104"/>
+      <c r="AB2" s="107"/>
+      <c r="AC2" s="107"/>
+      <c r="AD2" s="107"/>
+      <c r="AE2" s="107"/>
+      <c r="AF2" s="107"/>
+      <c r="AG2" s="107"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="104"/>
-      <c r="AJ2" s="104"/>
-      <c r="AK2" s="104"/>
-      <c r="AL2" s="104"/>
-      <c r="AM2" s="104"/>
-      <c r="AN2" s="102"/>
-      <c r="AO2" s="102"/>
-      <c r="AP2" s="104"/>
+      <c r="AI2" s="107"/>
+      <c r="AJ2" s="107"/>
+      <c r="AK2" s="107"/>
+      <c r="AL2" s="107"/>
+      <c r="AM2" s="107"/>
+      <c r="AN2" s="112"/>
+      <c r="AO2" s="112"/>
+      <c r="AP2" s="107"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="71">
@@ -32925,7 +33131,7 @@
       <c r="G229" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="H229" s="119" t="s">
+      <c r="H229" s="101" t="s">
         <v>89</v>
       </c>
       <c r="I229" s="7" t="s">
@@ -33059,7 +33265,7 @@
       <c r="G230" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="H230" s="119" t="s">
+      <c r="H230" s="101" t="s">
         <v>89</v>
       </c>
       <c r="I230" s="7" t="s">
@@ -33193,7 +33399,7 @@
       <c r="G231" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="H231" s="119" t="s">
+      <c r="H231" s="101" t="s">
         <v>89</v>
       </c>
       <c r="I231" s="7" t="s">
@@ -33327,7 +33533,7 @@
       <c r="G232" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="H232" s="119" t="s">
+      <c r="H232" s="101" t="s">
         <v>89</v>
       </c>
       <c r="I232" s="7" t="s">
@@ -33461,7 +33667,7 @@
       <c r="G233" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="H233" s="119" t="s">
+      <c r="H233" s="101" t="s">
         <v>89</v>
       </c>
       <c r="I233" s="7" t="s">
@@ -33595,7 +33801,7 @@
       <c r="G234" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="H234" s="119" t="s">
+      <c r="H234" s="101" t="s">
         <v>89</v>
       </c>
       <c r="I234" s="7" t="s">
@@ -33729,7 +33935,7 @@
       <c r="G235" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="H235" s="119" t="s">
+      <c r="H235" s="101" t="s">
         <v>90</v>
       </c>
       <c r="I235" s="7" t="s">
@@ -33863,7 +34069,7 @@
       <c r="G236" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="H236" s="119" t="s">
+      <c r="H236" s="101" t="s">
         <v>90</v>
       </c>
       <c r="I236" s="7" t="s">
@@ -33997,7 +34203,7 @@
       <c r="G237" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="H237" s="119" t="s">
+      <c r="H237" s="101" t="s">
         <v>90</v>
       </c>
       <c r="I237" s="7" t="s">
@@ -34131,7 +34337,7 @@
       <c r="G238" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="H238" s="119" t="s">
+      <c r="H238" s="101" t="s">
         <v>90</v>
       </c>
       <c r="I238" s="7" t="s">
@@ -34265,7 +34471,7 @@
       <c r="G239" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="H239" s="119" t="s">
+      <c r="H239" s="101" t="s">
         <v>104</v>
       </c>
       <c r="I239" s="7" t="s">
@@ -34399,7 +34605,7 @@
       <c r="G240" s="19" t="s">
         <v>375</v>
       </c>
-      <c r="H240" s="119" t="s">
+      <c r="H240" s="101" t="s">
         <v>104</v>
       </c>
       <c r="I240" s="7" t="s">
@@ -34533,7 +34739,7 @@
       <c r="G241" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="H241" s="119" t="s">
+      <c r="H241" s="101" t="s">
         <v>79</v>
       </c>
       <c r="I241" s="7" t="s">
@@ -34667,7 +34873,7 @@
       <c r="G242" s="19" t="s">
         <v>378</v>
       </c>
-      <c r="H242" s="119" t="s">
+      <c r="H242" s="101" t="s">
         <v>79</v>
       </c>
       <c r="I242" s="7" t="s">
@@ -34801,7 +35007,7 @@
       <c r="G243" s="19" t="s">
         <v>379</v>
       </c>
-      <c r="H243" s="119" t="s">
+      <c r="H243" s="101" t="s">
         <v>79</v>
       </c>
       <c r="I243" s="7" t="s">
@@ -34935,7 +35141,7 @@
       <c r="G244" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="H244" s="119" t="s">
+      <c r="H244" s="101" t="s">
         <v>79</v>
       </c>
       <c r="I244" s="7" t="s">
@@ -35069,7 +35275,7 @@
       <c r="G245" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="H245" s="119" t="s">
+      <c r="H245" s="101" t="s">
         <v>79</v>
       </c>
       <c r="I245" s="7" t="s">
@@ -35203,10 +35409,10 @@
       <c r="G246" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="H246" s="119" t="s">
+      <c r="H246" s="101" t="s">
         <v>382</v>
       </c>
-      <c r="I246" s="118" t="s">
+      <c r="I246" s="6" t="s">
         <v>387</v>
       </c>
       <c r="J246" s="55">
@@ -35337,10 +35543,10 @@
       <c r="G247" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="H247" s="119" t="s">
+      <c r="H247" s="101" t="s">
         <v>382</v>
       </c>
-      <c r="I247" s="118" t="s">
+      <c r="I247" s="6" t="s">
         <v>387</v>
       </c>
       <c r="J247" s="55">
@@ -35471,10 +35677,10 @@
       <c r="G248" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="H248" s="119" t="s">
+      <c r="H248" s="101" t="s">
         <v>382</v>
       </c>
-      <c r="I248" s="118" t="s">
+      <c r="I248" s="6" t="s">
         <v>387</v>
       </c>
       <c r="J248" s="55">
@@ -35605,10 +35811,10 @@
       <c r="G249" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="H249" s="119" t="s">
+      <c r="H249" s="101" t="s">
         <v>382</v>
       </c>
-      <c r="I249" s="118" t="s">
+      <c r="I249" s="6" t="s">
         <v>387</v>
       </c>
       <c r="J249" s="55">
@@ -35739,7 +35945,7 @@
       <c r="G250" s="19" t="s">
         <v>388</v>
       </c>
-      <c r="H250" s="119" t="s">
+      <c r="H250" s="101" t="s">
         <v>212</v>
       </c>
       <c r="I250" s="6"/>
@@ -35869,7 +36075,7 @@
       <c r="G251" s="19" t="s">
         <v>389</v>
       </c>
-      <c r="H251" s="119" t="s">
+      <c r="H251" s="101" t="s">
         <v>212</v>
       </c>
       <c r="I251" s="6"/>
@@ -36001,7 +36207,7 @@
       <c r="G252" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="H252" s="119" t="s">
+      <c r="H252" s="101" t="s">
         <v>90</v>
       </c>
       <c r="I252" s="6" t="s">
@@ -36127,7 +36333,7 @@
       <c r="G253" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="H253" s="119" t="s">
+      <c r="H253" s="101" t="s">
         <v>90</v>
       </c>
       <c r="I253" s="6" t="s">
@@ -36253,7 +36459,7 @@
       <c r="G254" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H254" s="119" t="s">
+      <c r="H254" s="101" t="s">
         <v>212</v>
       </c>
       <c r="I254" s="6" t="s">
@@ -39631,7 +39837,7 @@
     </row>
     <row r="281" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A281" s="71">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B281" s="72" t="s">
         <v>67</v>
@@ -39648,10 +39854,18 @@
       <c r="F281" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G281" s="19"/>
-      <c r="H281" s="19"/>
-      <c r="I281" s="6"/>
-      <c r="J281" s="55"/>
+      <c r="G281" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="H281" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="I281" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="J281" s="55">
+        <v>20</v>
+      </c>
       <c r="K281" s="20"/>
       <c r="L281" s="20"/>
       <c r="M281" s="20"/>
@@ -39668,7 +39882,7 @@
       </c>
       <c r="S281" s="18">
         <f t="shared" si="119"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T281" s="18">
         <f t="shared" si="122"/>
@@ -39713,39 +39927,39 @@
       </c>
       <c r="AE281" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>2238.1999999999998</v>
       </c>
       <c r="AF281" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG281" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>145.483</v>
       </c>
       <c r="AH281" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI281" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>2092.7169999999996</v>
       </c>
       <c r="AJ281" s="5">
         <v>0.18</v>
       </c>
       <c r="AK281" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>376.68905999999993</v>
       </c>
       <c r="AL281" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>2469.4060599999993</v>
       </c>
       <c r="AP281" s="12"/>
     </row>
     <row r="282" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A282" s="71">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B282" s="72" t="s">
         <v>67</v>
@@ -39762,16 +39976,28 @@
       <c r="F282" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G282" s="19"/>
-      <c r="H282" s="19"/>
-      <c r="I282" s="6"/>
+      <c r="G282" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="H282" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="I282" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="J282" s="55"/>
-      <c r="K282" s="18"/>
-      <c r="L282" s="18"/>
-      <c r="M282" s="18"/>
+      <c r="K282" s="18">
+        <v>20</v>
+      </c>
+      <c r="L282" s="18">
+        <v>20</v>
+      </c>
+      <c r="M282" s="18">
+        <v>20</v>
+      </c>
       <c r="N282" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O282" s="20"/>
       <c r="P282" s="20"/>
@@ -39782,23 +40008,23 @@
       </c>
       <c r="S282" s="18">
         <f t="shared" si="119"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="T282" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U282" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V282" s="18">
         <f t="shared" si="124"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W282" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X282" s="18">
         <f t="shared" si="125"/>
@@ -39827,14 +40053,14 @@
       </c>
       <c r="AE282" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>7506.15</v>
       </c>
       <c r="AF282" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG282" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>487.89974999999998</v>
       </c>
       <c r="AH282" s="64">
         <f t="shared" si="132"/>
@@ -39842,24 +40068,24 @@
       </c>
       <c r="AI282" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>7018.2502500000001</v>
       </c>
       <c r="AJ282" s="5">
         <v>0.18</v>
       </c>
       <c r="AK282" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1263.2850449999999</v>
       </c>
       <c r="AL282" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>8281.5352949999997</v>
       </c>
       <c r="AP282" s="12"/>
     </row>
     <row r="283" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A283" s="71">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B283" s="72" t="s">
         <v>67</v>
@@ -39876,59 +40102,77 @@
       <c r="F283" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G283" s="19"/>
-      <c r="H283" s="19"/>
-      <c r="I283" s="6"/>
+      <c r="G283" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="H283" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="I283" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="J283" s="55"/>
-      <c r="K283" s="18"/>
-      <c r="L283" s="20"/>
-      <c r="M283" s="20"/>
+      <c r="K283" s="18">
+        <v>80</v>
+      </c>
+      <c r="L283" s="20">
+        <v>40</v>
+      </c>
+      <c r="M283" s="20">
+        <v>80</v>
+      </c>
       <c r="N283" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O283" s="18"/>
-      <c r="P283" s="18"/>
-      <c r="Q283" s="18"/>
+        <v>200</v>
+      </c>
+      <c r="O283" s="18">
+        <v>40</v>
+      </c>
+      <c r="P283" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q283" s="18">
+        <v>80</v>
+      </c>
       <c r="R283" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="S283" s="18">
         <f t="shared" si="119"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="T283" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U283" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V283" s="18">
         <f t="shared" si="124"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W283" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X283" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y283" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z283" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA283" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AB283" s="8">
         <v>39.270000000000003</v>
@@ -39941,14 +40185,14 @@
       </c>
       <c r="AE283" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>36642.9</v>
       </c>
       <c r="AF283" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG283" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>2381.7885000000001</v>
       </c>
       <c r="AH283" s="64">
         <f t="shared" si="132"/>
@@ -39956,24 +40200,24 @@
       </c>
       <c r="AI283" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>34261.111499999999</v>
       </c>
       <c r="AJ283" s="5">
         <v>0.18</v>
       </c>
       <c r="AK283" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>6167.0000700000001</v>
       </c>
       <c r="AL283" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>40428.111570000001</v>
       </c>
       <c r="AP283" s="12"/>
     </row>
     <row r="284" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A284" s="71">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B284" s="72" t="s">
         <v>67</v>
@@ -39990,9 +40234,15 @@
       <c r="F284" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G284" s="19"/>
-      <c r="H284" s="19"/>
-      <c r="I284" s="6"/>
+      <c r="G284" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="H284" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I284" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="J284" s="55"/>
       <c r="K284" s="18"/>
       <c r="L284" s="18"/>
@@ -40001,16 +40251,22 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O284" s="18"/>
-      <c r="P284" s="18"/>
-      <c r="Q284" s="18"/>
+      <c r="O284" s="18">
+        <v>40</v>
+      </c>
+      <c r="P284" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q284" s="18">
+        <v>40</v>
+      </c>
       <c r="R284" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S284" s="18">
         <f t="shared" si="119"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="T284" s="18">
         <f t="shared" si="122"/>
@@ -40030,19 +40286,19 @@
       </c>
       <c r="X284" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y284" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z284" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA284" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB284" s="8">
         <v>39.270000000000003</v>
@@ -40055,14 +40311,14 @@
       </c>
       <c r="AE284" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>8716.7999999999993</v>
       </c>
       <c r="AF284" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG284" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>566.59199999999998</v>
       </c>
       <c r="AH284" s="64">
         <f t="shared" si="132"/>
@@ -40070,24 +40326,24 @@
       </c>
       <c r="AI284" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>8150.2079999999996</v>
       </c>
       <c r="AJ284" s="5">
         <v>0.18</v>
       </c>
       <c r="AK284" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1467.0374399999998</v>
       </c>
       <c r="AL284" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>9617.2454399999988</v>
       </c>
       <c r="AP284" s="12"/>
     </row>
     <row r="285" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A285" s="71">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B285" s="72" t="s">
         <v>67</v>
@@ -40101,17 +40357,33 @@
       <c r="E285" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="F285" s="19"/>
-      <c r="G285" s="19"/>
-      <c r="H285" s="19"/>
-      <c r="I285" s="6"/>
-      <c r="J285" s="55"/>
-      <c r="K285" s="18"/>
-      <c r="L285" s="20"/>
-      <c r="M285" s="18"/>
+      <c r="F285" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G285" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="H285" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I285" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="J285" s="55">
+        <v>40</v>
+      </c>
+      <c r="K285" s="18">
+        <v>14</v>
+      </c>
+      <c r="L285" s="20">
+        <v>14</v>
+      </c>
+      <c r="M285" s="18">
+        <v>12</v>
+      </c>
       <c r="N285" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O285" s="18"/>
       <c r="P285" s="20"/>
@@ -40122,23 +40394,23 @@
       </c>
       <c r="S285" s="18">
         <f t="shared" si="119"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T285" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U285" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V285" s="18">
         <f t="shared" si="124"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W285" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X285" s="18">
         <f t="shared" si="125"/>
@@ -40167,39 +40439,39 @@
       </c>
       <c r="AE285" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>9480.5</v>
       </c>
       <c r="AF285" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG285" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>616.23250000000007</v>
       </c>
       <c r="AH285" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI285" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>8864.2674999999999</v>
       </c>
       <c r="AJ285" s="5">
         <v>0.18</v>
       </c>
       <c r="AK285" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1595.5681499999998</v>
       </c>
       <c r="AL285" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>10459.835649999999</v>
       </c>
       <c r="AP285" s="12"/>
     </row>
     <row r="286" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A286" s="71">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B286" s="72" t="s">
         <v>67</v>
@@ -40213,10 +40485,18 @@
       <c r="E286" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="F286" s="19"/>
-      <c r="G286" s="19"/>
-      <c r="H286" s="19"/>
-      <c r="I286" s="6"/>
+      <c r="F286" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G286" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="H286" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I286" s="6" t="s">
+        <v>427</v>
+      </c>
       <c r="J286" s="55"/>
       <c r="K286" s="18"/>
       <c r="L286" s="18"/>
@@ -40225,12 +40505,18 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O286" s="18"/>
-      <c r="P286" s="18"/>
-      <c r="Q286" s="18"/>
+      <c r="O286" s="18">
+        <v>14</v>
+      </c>
+      <c r="P286" s="18">
+        <v>14</v>
+      </c>
+      <c r="Q286" s="18">
+        <v>12</v>
+      </c>
       <c r="R286" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S286" s="18"/>
       <c r="T286" s="18">
@@ -40251,19 +40537,19 @@
       </c>
       <c r="X286" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y286" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z286" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA286" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB286" s="8">
         <v>39.270000000000003</v>
@@ -40308,7 +40594,7 @@
     </row>
     <row r="287" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A287" s="71">
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="B287" s="72" t="s">
         <v>67</v>
@@ -40322,11 +40608,21 @@
       <c r="E287" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="F287" s="19"/>
-      <c r="G287" s="19"/>
-      <c r="H287" s="19"/>
-      <c r="I287" s="6"/>
-      <c r="J287" s="55"/>
+      <c r="F287" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G287" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="H287" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I287" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="J287" s="55" t="s">
+        <v>50</v>
+      </c>
       <c r="K287" s="18"/>
       <c r="L287" s="20"/>
       <c r="M287" s="18"/>
@@ -40334,12 +40630,18 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O287" s="20"/>
-      <c r="P287" s="20"/>
-      <c r="Q287" s="20"/>
+      <c r="O287" s="18">
+        <v>14</v>
+      </c>
+      <c r="P287" s="18">
+        <v>14</v>
+      </c>
+      <c r="Q287" s="18">
+        <v>12</v>
+      </c>
       <c r="R287" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S287" s="18"/>
       <c r="T287" s="18">
@@ -40360,19 +40662,19 @@
       </c>
       <c r="X287" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y287" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z287" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA287" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB287" s="8">
         <v>39.270000000000003</v>
@@ -40383,41 +40685,41 @@
       <c r="AD287" s="8">
         <v>72.64</v>
       </c>
-      <c r="AE287" s="9">
+      <c r="AE287" s="9" t="e">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AF287" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AG287" s="10">
+      <c r="AG287" s="10" t="e">
         <f t="shared" si="128"/>
-        <v>0</v>
-      </c>
-      <c r="AH287" s="64">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AH287" s="64" t="e">
         <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="AI287" s="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AI287" s="9" t="e">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AJ287" s="5">
         <v>0.18</v>
       </c>
-      <c r="AK287" s="11">
+      <c r="AK287" s="11" t="e">
         <f t="shared" si="134"/>
-        <v>0</v>
-      </c>
-      <c r="AL287" s="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AL287" s="9" t="e">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AP287" s="12"/>
     </row>
     <row r="288" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A288" s="71">
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="B288" s="72" t="s">
         <v>67</v>
@@ -40431,11 +40733,21 @@
       <c r="E288" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="F288" s="19"/>
-      <c r="G288" s="19"/>
-      <c r="H288" s="19"/>
-      <c r="I288" s="6"/>
-      <c r="J288" s="55"/>
+      <c r="F288" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G288" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="H288" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I288" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="J288" s="55">
+        <v>10</v>
+      </c>
       <c r="K288" s="18"/>
       <c r="L288" s="18"/>
       <c r="M288" s="18"/>
@@ -40494,39 +40806,39 @@
       </c>
       <c r="AE288" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF288" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG288" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH288" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI288" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ288" s="5">
         <v>0.18</v>
       </c>
       <c r="AK288" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL288" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP288" s="12"/>
     </row>
     <row r="289" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A289" s="71">
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="B289" s="72" t="s">
         <v>67</v>
@@ -40540,11 +40852,21 @@
       <c r="E289" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="F289" s="19"/>
-      <c r="G289" s="19"/>
-      <c r="H289" s="19"/>
-      <c r="I289" s="6"/>
-      <c r="J289" s="55"/>
+      <c r="F289" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G289" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="H289" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I289" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="J289" s="55">
+        <v>10</v>
+      </c>
       <c r="K289" s="18"/>
       <c r="L289" s="18"/>
       <c r="M289" s="18"/>
@@ -40603,39 +40925,39 @@
       </c>
       <c r="AE289" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF289" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG289" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH289" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI289" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ289" s="5">
         <v>0.18</v>
       </c>
       <c r="AK289" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL289" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP289" s="12"/>
     </row>
     <row r="290" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A290" s="71">
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="B290" s="72" t="s">
         <v>67</v>
@@ -40649,11 +40971,21 @@
       <c r="E290" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="F290" s="19"/>
-      <c r="G290" s="19"/>
-      <c r="H290" s="19"/>
-      <c r="I290" s="6"/>
-      <c r="J290" s="55"/>
+      <c r="F290" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G290" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="H290" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I290" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="J290" s="55">
+        <v>10</v>
+      </c>
       <c r="K290" s="18"/>
       <c r="L290" s="18"/>
       <c r="M290" s="18"/>
@@ -40712,39 +41044,39 @@
       </c>
       <c r="AE290" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF290" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG290" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH290" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI290" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ290" s="5">
         <v>0.18</v>
       </c>
       <c r="AK290" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL290" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP290" s="12"/>
     </row>
     <row r="291" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A291" s="71">
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="B291" s="72" t="s">
         <v>67</v>
@@ -40758,11 +41090,21 @@
       <c r="E291" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="F291" s="19"/>
-      <c r="G291" s="19"/>
-      <c r="H291" s="19"/>
-      <c r="I291" s="6"/>
-      <c r="J291" s="55"/>
+      <c r="F291" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G291" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="H291" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I291" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="J291" s="55">
+        <v>10</v>
+      </c>
       <c r="K291" s="18"/>
       <c r="L291" s="18"/>
       <c r="M291" s="18"/>
@@ -40821,67 +41163,95 @@
       </c>
       <c r="AE291" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF291" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG291" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH291" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI291" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ291" s="5">
         <v>0.18</v>
       </c>
       <c r="AK291" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL291" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP291" s="12"/>
     </row>
     <row r="292" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A292" s="17"/>
-      <c r="C292" s="18"/>
-      <c r="E292" s="6"/>
-      <c r="F292" s="19"/>
-      <c r="G292" s="19"/>
-      <c r="H292" s="19"/>
-      <c r="I292" s="6"/>
+      <c r="A292" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B292" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C292" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D292" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E292" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F292" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G292" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="H292" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I292" s="6" t="s">
+        <v>431</v>
+      </c>
       <c r="J292" s="55"/>
-      <c r="K292" s="18"/>
-      <c r="L292" s="18"/>
+      <c r="K292" s="18">
+        <v>10</v>
+      </c>
+      <c r="L292" s="18">
+        <v>10</v>
+      </c>
       <c r="M292" s="18"/>
       <c r="N292" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O292" s="18"/>
-      <c r="P292" s="18"/>
+        <v>20</v>
+      </c>
+      <c r="O292" s="18">
+        <v>10</v>
+      </c>
+      <c r="P292" s="18">
+        <v>10</v>
+      </c>
       <c r="Q292" s="18"/>
       <c r="R292" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S292" s="18"/>
       <c r="T292" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U292" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V292" s="18">
         <f t="shared" si="124"/>
@@ -40889,15 +41259,15 @@
       </c>
       <c r="W292" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X292" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y292" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z292" s="18">
         <f t="shared" si="127"/>
@@ -40905,7 +41275,7 @@
       </c>
       <c r="AA292" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB292" s="8">
         <v>39.270000000000003</v>
@@ -40918,14 +41288,14 @@
       </c>
       <c r="AE292" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>1049.25</v>
       </c>
       <c r="AF292" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG292" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>68.201250000000002</v>
       </c>
       <c r="AH292" s="64">
         <f t="shared" si="132"/>
@@ -40933,29 +41303,49 @@
       </c>
       <c r="AI292" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>981.04875000000004</v>
       </c>
       <c r="AJ292" s="5">
         <v>0.18</v>
       </c>
       <c r="AK292" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>176.588775</v>
       </c>
       <c r="AL292" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>1157.6375250000001</v>
       </c>
       <c r="AP292" s="12"/>
     </row>
     <row r="293" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A293" s="17"/>
-      <c r="C293" s="18"/>
-      <c r="E293" s="6"/>
-      <c r="F293" s="19"/>
-      <c r="G293" s="19"/>
-      <c r="H293" s="19"/>
-      <c r="I293" s="6"/>
+      <c r="A293" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B293" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C293" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D293" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E293" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F293" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G293" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="H293" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I293" s="6" t="s">
+        <v>431</v>
+      </c>
       <c r="J293" s="55"/>
       <c r="K293" s="20"/>
       <c r="L293" s="20"/>
@@ -40964,12 +41354,18 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O293" s="18"/>
-      <c r="P293" s="18"/>
-      <c r="Q293" s="18"/>
+      <c r="O293" s="18">
+        <v>5</v>
+      </c>
+      <c r="P293" s="18">
+        <v>5</v>
+      </c>
+      <c r="Q293" s="18">
+        <v>10</v>
+      </c>
       <c r="R293" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S293" s="18"/>
       <c r="T293" s="18">
@@ -40990,19 +41386,19 @@
       </c>
       <c r="X293" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y293" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z293" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA293" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB293" s="8">
         <v>39.270000000000003</v>
@@ -41046,60 +41442,92 @@
       <c r="AP293" s="12"/>
     </row>
     <row r="294" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A294" s="17"/>
-      <c r="C294" s="18"/>
-      <c r="E294" s="6"/>
-      <c r="F294" s="19"/>
-      <c r="G294" s="19"/>
-      <c r="H294" s="19"/>
-      <c r="I294" s="6"/>
+      <c r="A294" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B294" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C294" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D294" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E294" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F294" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G294" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="H294" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I294" s="6" t="s">
+        <v>431</v>
+      </c>
       <c r="J294" s="55"/>
-      <c r="K294" s="20"/>
-      <c r="L294" s="20"/>
-      <c r="M294" s="20"/>
+      <c r="K294" s="20">
+        <v>15</v>
+      </c>
+      <c r="L294" s="20">
+        <v>15</v>
+      </c>
+      <c r="M294" s="20">
+        <v>10</v>
+      </c>
       <c r="N294" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O294" s="18"/>
-      <c r="P294" s="18"/>
-      <c r="Q294" s="18"/>
+        <v>40</v>
+      </c>
+      <c r="O294" s="18">
+        <v>15</v>
+      </c>
+      <c r="P294" s="18">
+        <v>15</v>
+      </c>
+      <c r="Q294" s="18">
+        <v>10</v>
+      </c>
       <c r="R294" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S294" s="18"/>
       <c r="T294" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U294" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V294" s="18">
         <f t="shared" si="124"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W294" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X294" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y294" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z294" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA294" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB294" s="8">
         <v>39.270000000000003</v>
@@ -41112,14 +41540,14 @@
       </c>
       <c r="AE294" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>2098.5</v>
       </c>
       <c r="AF294" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG294" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>136.4025</v>
       </c>
       <c r="AH294" s="64">
         <f t="shared" si="132"/>
@@ -41127,52 +41555,84 @@
       </c>
       <c r="AI294" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>1962.0975000000001</v>
       </c>
       <c r="AJ294" s="5">
         <v>0.18</v>
       </c>
       <c r="AK294" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>353.17755</v>
       </c>
       <c r="AL294" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>2315.2750500000002</v>
       </c>
       <c r="AP294" s="12"/>
     </row>
     <row r="295" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A295" s="17"/>
-      <c r="C295" s="18"/>
-      <c r="E295" s="6"/>
-      <c r="F295" s="19"/>
-      <c r="G295" s="19"/>
-      <c r="H295" s="19"/>
-      <c r="I295" s="6"/>
-      <c r="J295" s="55"/>
-      <c r="K295" s="20"/>
-      <c r="L295" s="20"/>
+      <c r="A295" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B295" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C295" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D295" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E295" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F295" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G295" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="H295" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I295" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="J295" s="55">
+        <v>80</v>
+      </c>
+      <c r="K295" s="20">
+        <v>80</v>
+      </c>
+      <c r="L295" s="20">
+        <v>40</v>
+      </c>
       <c r="M295" s="20"/>
       <c r="N295" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O295" s="18"/>
-      <c r="P295" s="18"/>
-      <c r="Q295" s="18"/>
+        <v>120</v>
+      </c>
+      <c r="O295" s="18">
+        <v>40</v>
+      </c>
+      <c r="P295" s="18">
+        <v>20</v>
+      </c>
+      <c r="Q295" s="18">
+        <v>60</v>
+      </c>
       <c r="R295" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S295" s="18"/>
       <c r="T295" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U295" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V295" s="18">
         <f t="shared" si="124"/>
@@ -41180,23 +41640,23 @@
       </c>
       <c r="W295" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X295" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y295" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z295" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA295" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB295" s="8">
         <v>39.270000000000003</v>
@@ -41209,44 +41669,64 @@
       </c>
       <c r="AE295" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>9437.1</v>
       </c>
       <c r="AF295" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG295" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>613.41150000000005</v>
       </c>
       <c r="AH295" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI295" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>8823.6885000000002</v>
       </c>
       <c r="AJ295" s="5">
         <v>0.18</v>
       </c>
       <c r="AK295" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1588.2639300000001</v>
       </c>
       <c r="AL295" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>10411.952430000001</v>
       </c>
       <c r="AP295" s="12"/>
     </row>
     <row r="296" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A296" s="17"/>
-      <c r="C296" s="18"/>
-      <c r="E296" s="6"/>
-      <c r="F296" s="19"/>
-      <c r="G296" s="19"/>
-      <c r="H296" s="19"/>
-      <c r="I296" s="6"/>
+      <c r="A296" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B296" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C296" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D296" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E296" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F296" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G296" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="H296" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I296" s="6" t="s">
+        <v>278</v>
+      </c>
       <c r="J296" s="55"/>
       <c r="K296" s="18"/>
       <c r="L296" s="18"/>
@@ -41255,12 +41735,18 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O296" s="20"/>
-      <c r="P296" s="20"/>
-      <c r="Q296" s="20"/>
+      <c r="O296" s="20">
+        <v>13</v>
+      </c>
+      <c r="P296" s="20">
+        <v>13</v>
+      </c>
+      <c r="Q296" s="20">
+        <v>14</v>
+      </c>
       <c r="R296" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S296" s="18"/>
       <c r="T296" s="18">
@@ -41281,19 +41767,19 @@
       </c>
       <c r="X296" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Y296" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z296" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA296" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB296" s="8">
         <v>39.270000000000003</v>
@@ -41337,60 +41823,92 @@
       <c r="AP296" s="12"/>
     </row>
     <row r="297" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A297" s="17"/>
-      <c r="C297" s="18"/>
-      <c r="E297" s="6"/>
-      <c r="F297" s="19"/>
-      <c r="G297" s="19"/>
-      <c r="H297" s="19"/>
-      <c r="I297" s="6"/>
+      <c r="A297" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B297" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C297" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D297" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E297" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F297" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G297" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="H297" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I297" s="6" t="s">
+        <v>441</v>
+      </c>
       <c r="J297" s="55"/>
-      <c r="K297" s="18"/>
-      <c r="L297" s="18"/>
-      <c r="M297" s="18"/>
+      <c r="K297" s="18">
+        <v>120</v>
+      </c>
+      <c r="L297" s="18">
+        <v>120</v>
+      </c>
+      <c r="M297" s="18">
+        <v>80</v>
+      </c>
       <c r="N297" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O297" s="18"/>
-      <c r="P297" s="18"/>
-      <c r="Q297" s="18"/>
+        <v>320</v>
+      </c>
+      <c r="O297" s="18">
+        <v>120</v>
+      </c>
+      <c r="P297" s="18">
+        <v>120</v>
+      </c>
+      <c r="Q297" s="18">
+        <v>80</v>
+      </c>
       <c r="R297" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="S297" s="18"/>
       <c r="T297" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U297" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V297" s="18">
         <f t="shared" si="124"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W297" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="X297" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y297" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z297" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA297" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB297" s="8">
         <v>39.270000000000003</v>
@@ -41403,14 +41921,14 @@
       </c>
       <c r="AE297" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>16788</v>
       </c>
       <c r="AF297" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG297" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>1091.22</v>
       </c>
       <c r="AH297" s="64">
         <f t="shared" si="132"/>
@@ -41418,29 +41936,49 @@
       </c>
       <c r="AI297" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>15696.78</v>
       </c>
       <c r="AJ297" s="5">
         <v>0.18</v>
       </c>
       <c r="AK297" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>2825.4204</v>
       </c>
       <c r="AL297" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>18522.200400000002</v>
       </c>
       <c r="AP297" s="12"/>
     </row>
     <row r="298" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A298" s="17"/>
-      <c r="C298" s="18"/>
-      <c r="E298" s="6"/>
-      <c r="F298" s="19"/>
-      <c r="G298" s="19"/>
-      <c r="H298" s="19"/>
-      <c r="I298" s="6"/>
+      <c r="A298" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B298" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C298" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D298" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E298" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F298" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G298" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="H298" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="I298" s="6" t="s">
+        <v>294</v>
+      </c>
       <c r="J298" s="55"/>
       <c r="K298" s="18"/>
       <c r="L298" s="20"/>
@@ -41451,10 +41989,12 @@
       </c>
       <c r="O298" s="18"/>
       <c r="P298" s="18"/>
-      <c r="Q298" s="18"/>
+      <c r="Q298" s="18">
+        <v>40</v>
+      </c>
       <c r="R298" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S298" s="18"/>
       <c r="T298" s="18">
@@ -41483,11 +42023,11 @@
       </c>
       <c r="Z298" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA298" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB298" s="8">
         <v>39.270000000000003</v>
@@ -41531,13 +42071,33 @@
       <c r="AP298" s="12"/>
     </row>
     <row r="299" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A299" s="17"/>
-      <c r="C299" s="18"/>
-      <c r="E299" s="6"/>
-      <c r="F299" s="19"/>
-      <c r="G299" s="19"/>
-      <c r="H299" s="19"/>
-      <c r="I299" s="6"/>
+      <c r="A299" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B299" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C299" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D299" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E299" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F299" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G299" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="H299" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="I299" s="6" t="s">
+        <v>443</v>
+      </c>
       <c r="J299" s="55"/>
       <c r="K299" s="20"/>
       <c r="L299" s="20"/>
@@ -41547,11 +42107,13 @@
         <v>0</v>
       </c>
       <c r="O299" s="18"/>
-      <c r="P299" s="18"/>
+      <c r="P299" s="18">
+        <v>24</v>
+      </c>
       <c r="Q299" s="18"/>
       <c r="R299" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S299" s="18"/>
       <c r="T299" s="18">
@@ -41576,7 +42138,7 @@
       </c>
       <c r="Y299" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z299" s="18">
         <f t="shared" si="127"/>
@@ -41584,7 +42146,7 @@
       </c>
       <c r="AA299" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB299" s="8">
         <v>39.270000000000003</v>
@@ -41628,14 +42190,36 @@
       <c r="AP299" s="12"/>
     </row>
     <row r="300" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A300" s="17"/>
-      <c r="C300" s="18"/>
-      <c r="E300" s="6"/>
-      <c r="F300" s="19"/>
-      <c r="G300" s="19"/>
-      <c r="H300" s="19"/>
-      <c r="I300" s="6"/>
-      <c r="J300" s="55"/>
+      <c r="A300" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B300" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C300" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D300" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E300" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F300" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G300" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="H300" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="I300" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="J300" s="55">
+        <v>40</v>
+      </c>
       <c r="K300" s="20"/>
       <c r="L300" s="20"/>
       <c r="M300" s="20"/>
@@ -41645,10 +42229,12 @@
       </c>
       <c r="O300" s="18"/>
       <c r="P300" s="18"/>
-      <c r="Q300" s="18"/>
+      <c r="Q300" s="18">
+        <v>6</v>
+      </c>
       <c r="R300" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S300" s="18"/>
       <c r="T300" s="18">
@@ -41677,11 +42263,11 @@
       </c>
       <c r="Z300" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AA300" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AB300" s="8">
         <v>39.270000000000003</v>
@@ -41694,45 +42280,67 @@
       </c>
       <c r="AE300" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>1570.8000000000002</v>
       </c>
       <c r="AF300" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG300" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>102.10200000000002</v>
       </c>
       <c r="AH300" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI300" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>1468.6980000000001</v>
       </c>
       <c r="AJ300" s="5">
         <v>0.18</v>
       </c>
       <c r="AK300" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>264.36563999999998</v>
       </c>
       <c r="AL300" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>1733.0636400000001</v>
       </c>
       <c r="AP300" s="12"/>
     </row>
     <row r="301" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A301" s="17"/>
-      <c r="C301" s="18"/>
-      <c r="E301" s="6"/>
-      <c r="F301" s="19"/>
-      <c r="G301" s="19"/>
-      <c r="H301" s="19"/>
-      <c r="I301" s="6"/>
-      <c r="J301" s="55"/>
+      <c r="A301" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B301" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C301" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D301" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E301" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F301" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G301" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="H301" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="I301" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="J301" s="55">
+        <v>12</v>
+      </c>
       <c r="K301" s="18"/>
       <c r="L301" s="18"/>
       <c r="M301" s="18"/>
@@ -41740,12 +42348,18 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O301" s="20"/>
-      <c r="P301" s="20"/>
-      <c r="Q301" s="20"/>
+      <c r="O301" s="20">
+        <v>20</v>
+      </c>
+      <c r="P301" s="20">
+        <v>5</v>
+      </c>
+      <c r="Q301" s="20">
+        <v>15</v>
+      </c>
       <c r="R301" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S301" s="18"/>
       <c r="T301" s="18">
@@ -41766,19 +42380,19 @@
       </c>
       <c r="X301" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y301" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z301" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA301" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB301" s="8">
         <v>39.270000000000003</v>
@@ -41791,45 +42405,67 @@
       </c>
       <c r="AE301" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>471.24</v>
       </c>
       <c r="AF301" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG301" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>30.630600000000001</v>
       </c>
       <c r="AH301" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI301" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>440.60939999999999</v>
       </c>
       <c r="AJ301" s="5">
         <v>0.18</v>
       </c>
       <c r="AK301" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>79.309691999999998</v>
       </c>
       <c r="AL301" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>519.91909199999998</v>
       </c>
       <c r="AP301" s="12"/>
     </row>
     <row r="302" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A302" s="17"/>
-      <c r="C302" s="18"/>
-      <c r="E302" s="6"/>
-      <c r="F302" s="19"/>
-      <c r="G302" s="19"/>
-      <c r="H302" s="19"/>
-      <c r="I302" s="6"/>
-      <c r="J302" s="55"/>
+      <c r="A302" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B302" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C302" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D302" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E302" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F302" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G302" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="H302" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="I302" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="J302" s="55">
+        <v>20</v>
+      </c>
       <c r="K302" s="18"/>
       <c r="L302" s="18"/>
       <c r="M302" s="18"/>
@@ -41837,12 +42473,18 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O302" s="18"/>
-      <c r="P302" s="18"/>
-      <c r="Q302" s="18"/>
+      <c r="O302" s="18">
+        <v>10</v>
+      </c>
+      <c r="P302" s="18">
+        <v>5</v>
+      </c>
+      <c r="Q302" s="18">
+        <v>5</v>
+      </c>
       <c r="R302" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S302" s="18"/>
       <c r="T302" s="18">
@@ -41863,19 +42505,19 @@
       </c>
       <c r="X302" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y302" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z302" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AA302" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB302" s="8">
         <v>39.270000000000003</v>
@@ -41888,67 +42530,93 @@
       </c>
       <c r="AE302" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>785.40000000000009</v>
       </c>
       <c r="AF302" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG302" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>51.051000000000009</v>
       </c>
       <c r="AH302" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI302" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>734.34900000000005</v>
       </c>
       <c r="AJ302" s="5">
         <v>0.18</v>
       </c>
       <c r="AK302" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>132.18281999999999</v>
       </c>
       <c r="AL302" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>866.53182000000004</v>
       </c>
       <c r="AP302" s="12"/>
     </row>
     <row r="303" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A303" s="17"/>
-      <c r="C303" s="18"/>
-      <c r="E303" s="6"/>
-      <c r="F303" s="19"/>
-      <c r="G303" s="19"/>
-      <c r="H303" s="19"/>
-      <c r="I303" s="6"/>
+      <c r="A303" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B303" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C303" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D303" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E303" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F303" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G303" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="H303" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I303" s="6" t="s">
+        <v>449</v>
+      </c>
       <c r="J303" s="55"/>
-      <c r="K303" s="18"/>
-      <c r="L303" s="18"/>
+      <c r="K303" s="18">
+        <v>20</v>
+      </c>
+      <c r="L303" s="18">
+        <v>20</v>
+      </c>
       <c r="M303" s="18"/>
       <c r="N303" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O303" s="18"/>
       <c r="P303" s="18"/>
-      <c r="Q303" s="18"/>
+      <c r="Q303" s="18">
+        <v>6</v>
+      </c>
       <c r="R303" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S303" s="18"/>
       <c r="T303" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U303" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V303" s="18">
         <f t="shared" si="124"/>
@@ -41956,7 +42624,7 @@
       </c>
       <c r="W303" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X303" s="18">
         <f t="shared" si="125"/>
@@ -41968,11 +42636,11 @@
       </c>
       <c r="Z303" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AA303" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AB303" s="8">
         <v>39.270000000000003</v>
@@ -41985,14 +42653,14 @@
       </c>
       <c r="AE303" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>2098.5</v>
       </c>
       <c r="AF303" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG303" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>136.4025</v>
       </c>
       <c r="AH303" s="64">
         <f t="shared" si="132"/>
@@ -42000,36 +42668,62 @@
       </c>
       <c r="AI303" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>1962.0975000000001</v>
       </c>
       <c r="AJ303" s="5">
         <v>0.18</v>
       </c>
       <c r="AK303" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>353.17755</v>
       </c>
       <c r="AL303" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>2315.2750500000002</v>
       </c>
       <c r="AP303" s="12"/>
     </row>
     <row r="304" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A304" s="17"/>
-      <c r="C304" s="18"/>
-      <c r="E304" s="6"/>
-      <c r="F304" s="19"/>
-      <c r="G304" s="19"/>
-      <c r="H304" s="19"/>
-      <c r="I304" s="6"/>
-      <c r="J304" s="55"/>
-      <c r="K304" s="20"/>
-      <c r="L304" s="20"/>
+      <c r="A304" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B304" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C304" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D304" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E304" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F304" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G304" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="H304" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I304" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="J304" s="55">
+        <v>40</v>
+      </c>
+      <c r="K304" s="20">
+        <v>10</v>
+      </c>
+      <c r="L304" s="20">
+        <v>10</v>
+      </c>
       <c r="M304" s="20"/>
       <c r="N304" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O304" s="18"/>
       <c r="P304" s="18"/>
@@ -42041,11 +42735,11 @@
       <c r="S304" s="18"/>
       <c r="T304" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U304" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V304" s="18">
         <f t="shared" si="124"/>
@@ -42053,7 +42747,7 @@
       </c>
       <c r="W304" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X304" s="18">
         <f t="shared" si="125"/>
@@ -42082,44 +42776,64 @@
       </c>
       <c r="AE304" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>2620.0500000000002</v>
       </c>
       <c r="AF304" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG304" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>170.30325000000002</v>
       </c>
       <c r="AH304" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI304" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>2449.7467500000002</v>
       </c>
       <c r="AJ304" s="5">
         <v>0.18</v>
       </c>
       <c r="AK304" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>440.95441500000004</v>
       </c>
       <c r="AL304" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>2890.7011650000004</v>
       </c>
       <c r="AP304" s="12"/>
     </row>
     <row r="305" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A305" s="17"/>
-      <c r="C305" s="18"/>
-      <c r="E305" s="6"/>
-      <c r="F305" s="19"/>
-      <c r="G305" s="19"/>
-      <c r="H305" s="19"/>
-      <c r="I305" s="6"/>
+      <c r="A305" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B305" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C305" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D305" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E305" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F305" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G305" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="H305" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I305" s="6" t="s">
+        <v>449</v>
+      </c>
       <c r="J305" s="55"/>
       <c r="K305" s="20"/>
       <c r="L305" s="20"/>
@@ -42128,12 +42842,14 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O305" s="18"/>
+      <c r="O305" s="18">
+        <v>20</v>
+      </c>
       <c r="P305" s="18"/>
       <c r="Q305" s="18"/>
       <c r="R305" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S305" s="18"/>
       <c r="T305" s="18">
@@ -42154,7 +42870,7 @@
       </c>
       <c r="X305" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y305" s="18">
         <f t="shared" si="126"/>
@@ -42166,7 +42882,7 @@
       </c>
       <c r="AA305" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB305" s="8">
         <v>39.270000000000003</v>
@@ -42210,36 +42926,68 @@
       <c r="AP305" s="12"/>
     </row>
     <row r="306" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A306" s="17"/>
-      <c r="C306" s="18"/>
-      <c r="E306" s="6"/>
-      <c r="F306" s="19"/>
-      <c r="G306" s="19"/>
-      <c r="H306" s="19"/>
-      <c r="I306" s="6"/>
-      <c r="J306" s="55"/>
-      <c r="K306" s="18"/>
-      <c r="L306" s="18"/>
+      <c r="A306" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B306" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C306" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D306" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E306" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F306" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G306" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="H306" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I306" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="J306" s="55">
+        <v>10</v>
+      </c>
+      <c r="K306" s="18">
+        <v>10</v>
+      </c>
+      <c r="L306" s="18">
+        <v>10</v>
+      </c>
       <c r="M306" s="18"/>
       <c r="N306" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O306" s="18"/>
-      <c r="P306" s="18"/>
-      <c r="Q306" s="18"/>
+        <v>20</v>
+      </c>
+      <c r="O306" s="18">
+        <v>14</v>
+      </c>
+      <c r="P306" s="18">
+        <v>13</v>
+      </c>
+      <c r="Q306" s="18">
+        <v>13</v>
+      </c>
       <c r="R306" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S306" s="18"/>
       <c r="T306" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U306" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V306" s="18">
         <f t="shared" si="124"/>
@@ -42247,23 +42995,23 @@
       </c>
       <c r="W306" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X306" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y306" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z306" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA306" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB306" s="8">
         <v>39.270000000000003</v>
@@ -42276,45 +43024,67 @@
       </c>
       <c r="AE306" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>1441.95</v>
       </c>
       <c r="AF306" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG306" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>201.87300000000002</v>
       </c>
       <c r="AH306" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI306" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>1240.077</v>
       </c>
       <c r="AJ306" s="5">
         <v>0.18</v>
       </c>
       <c r="AK306" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>223.21385999999998</v>
       </c>
       <c r="AL306" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>1463.2908600000001</v>
       </c>
       <c r="AP306" s="12"/>
     </row>
     <row r="307" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A307" s="17"/>
-      <c r="C307" s="18"/>
-      <c r="E307" s="6"/>
-      <c r="F307" s="19"/>
-      <c r="G307" s="19"/>
-      <c r="H307" s="19"/>
-      <c r="I307" s="6"/>
-      <c r="J307" s="55"/>
+      <c r="A307" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B307" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C307" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D307" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E307" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F307" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G307" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="H307" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I307" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="J307" s="55">
+        <v>40</v>
+      </c>
       <c r="K307" s="18"/>
       <c r="L307" s="18"/>
       <c r="M307" s="18"/>
@@ -42324,10 +43094,12 @@
       </c>
       <c r="O307" s="18"/>
       <c r="P307" s="18"/>
-      <c r="Q307" s="18"/>
+      <c r="Q307" s="18">
+        <v>24</v>
+      </c>
       <c r="R307" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S307" s="18"/>
       <c r="T307" s="18">
@@ -42356,11 +43128,11 @@
       </c>
       <c r="Z307" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA307" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB307" s="8">
         <v>39.270000000000003</v>
@@ -42373,67 +43145,99 @@
       </c>
       <c r="AE307" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>1570.8000000000002</v>
       </c>
       <c r="AF307" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG307" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>102.10200000000002</v>
       </c>
       <c r="AH307" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI307" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>1468.6980000000001</v>
       </c>
       <c r="AJ307" s="5">
         <v>0.18</v>
       </c>
       <c r="AK307" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>264.36563999999998</v>
       </c>
       <c r="AL307" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>1733.0636400000001</v>
       </c>
       <c r="AP307" s="12"/>
     </row>
     <row r="308" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A308" s="17"/>
-      <c r="C308" s="18"/>
-      <c r="E308" s="6"/>
-      <c r="F308" s="19"/>
-      <c r="G308" s="19"/>
-      <c r="H308" s="19"/>
-      <c r="I308" s="6"/>
-      <c r="J308" s="55"/>
-      <c r="K308" s="20"/>
-      <c r="L308" s="20"/>
+      <c r="A308" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B308" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C308" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D308" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E308" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F308" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G308" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="H308" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I308" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="J308" s="55">
+        <v>40</v>
+      </c>
+      <c r="K308" s="20">
+        <v>20</v>
+      </c>
+      <c r="L308" s="20">
+        <v>40</v>
+      </c>
       <c r="M308" s="20"/>
       <c r="N308" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O308" s="18"/>
-      <c r="P308" s="18"/>
-      <c r="Q308" s="18"/>
+        <v>60</v>
+      </c>
+      <c r="O308" s="18">
+        <v>20</v>
+      </c>
+      <c r="P308" s="18">
+        <v>20</v>
+      </c>
+      <c r="Q308" s="18">
+        <v>20</v>
+      </c>
       <c r="R308" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S308" s="18"/>
       <c r="T308" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U308" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V308" s="18">
         <f t="shared" si="124"/>
@@ -42441,23 +43245,23 @@
       </c>
       <c r="W308" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X308" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y308" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z308" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA308" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB308" s="8">
         <v>39.270000000000003</v>
@@ -42470,44 +43274,64 @@
       </c>
       <c r="AE308" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>4718.55</v>
       </c>
       <c r="AF308" s="21">
         <v>0.13</v>
       </c>
       <c r="AG308" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>613.41150000000005</v>
       </c>
       <c r="AH308" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI308" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>4105.1385</v>
       </c>
       <c r="AJ308" s="5">
         <v>0.18</v>
       </c>
       <c r="AK308" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>738.92493000000002</v>
       </c>
       <c r="AL308" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>4844.0634300000002</v>
       </c>
       <c r="AP308" s="12"/>
     </row>
     <row r="309" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A309" s="17"/>
-      <c r="C309" s="18"/>
-      <c r="E309" s="6"/>
-      <c r="F309" s="19"/>
-      <c r="G309" s="19"/>
-      <c r="H309" s="19"/>
-      <c r="I309" s="6"/>
+      <c r="A309" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B309" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C309" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D309" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E309" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F309" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G309" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="H309" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I309" s="6" t="s">
+        <v>456</v>
+      </c>
       <c r="J309" s="55"/>
       <c r="K309" s="18"/>
       <c r="L309" s="18"/>
@@ -42516,12 +43340,18 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O309" s="18"/>
-      <c r="P309" s="18"/>
-      <c r="Q309" s="18"/>
+      <c r="O309" s="18">
+        <v>20</v>
+      </c>
+      <c r="P309" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q309" s="18">
+        <v>10</v>
+      </c>
       <c r="R309" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S309" s="18"/>
       <c r="T309" s="18">
@@ -42542,19 +43372,19 @@
       </c>
       <c r="X309" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y309" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z309" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA309" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB309" s="8">
         <v>39.270000000000003</v>
@@ -42598,36 +43428,66 @@
       <c r="AP309" s="12"/>
     </row>
     <row r="310" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A310" s="17"/>
-      <c r="C310" s="18"/>
-      <c r="E310" s="6"/>
-      <c r="F310" s="19"/>
-      <c r="G310" s="19"/>
-      <c r="H310" s="19"/>
-      <c r="I310" s="6"/>
+      <c r="A310" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B310" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C310" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D310" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E310" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F310" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G310" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="H310" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I310" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="J310" s="55"/>
-      <c r="K310" s="20"/>
-      <c r="L310" s="20"/>
+      <c r="K310" s="20">
+        <v>10</v>
+      </c>
+      <c r="L310" s="20">
+        <v>10</v>
+      </c>
       <c r="M310" s="18"/>
       <c r="N310" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O310" s="18"/>
-      <c r="P310" s="18"/>
-      <c r="Q310" s="18"/>
+        <v>20</v>
+      </c>
+      <c r="O310" s="18">
+        <v>15</v>
+      </c>
+      <c r="P310" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q310" s="18">
+        <v>15</v>
+      </c>
       <c r="R310" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S310" s="18"/>
       <c r="T310" s="18">
         <f t="shared" si="122"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U310" s="18">
         <f t="shared" si="123"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V310" s="18">
         <f t="shared" si="124"/>
@@ -42635,23 +43495,23 @@
       </c>
       <c r="W310" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X310" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y310" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z310" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA310" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB310" s="8">
         <v>39.270000000000003</v>
@@ -42664,14 +43524,14 @@
       </c>
       <c r="AE310" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>1049.25</v>
       </c>
       <c r="AF310" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG310" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>68.201250000000002</v>
       </c>
       <c r="AH310" s="64">
         <f t="shared" si="132"/>
@@ -42679,30 +43539,52 @@
       </c>
       <c r="AI310" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>981.04875000000004</v>
       </c>
       <c r="AJ310" s="5">
         <v>0.18</v>
       </c>
       <c r="AK310" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>176.588775</v>
       </c>
       <c r="AL310" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>1157.6375250000001</v>
       </c>
       <c r="AP310" s="12"/>
     </row>
     <row r="311" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A311" s="17"/>
-      <c r="C311" s="18"/>
-      <c r="E311" s="6"/>
-      <c r="F311" s="19"/>
-      <c r="G311" s="19"/>
-      <c r="H311" s="19"/>
-      <c r="I311" s="6"/>
-      <c r="J311" s="55"/>
+      <c r="A311" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B311" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C311" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D311" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E311" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F311" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G311" s="19" t="s">
+        <v>459</v>
+      </c>
+      <c r="H311" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I311" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J311" s="55">
+        <v>10</v>
+      </c>
       <c r="K311" s="18"/>
       <c r="L311" s="18"/>
       <c r="M311" s="18"/>
@@ -42761,45 +43643,67 @@
       </c>
       <c r="AE311" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF311" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG311" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH311" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI311" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ311" s="5">
         <v>0.18</v>
       </c>
       <c r="AK311" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL311" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP311" s="12"/>
     </row>
     <row r="312" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A312" s="17"/>
-      <c r="C312" s="18"/>
-      <c r="E312" s="6"/>
-      <c r="F312" s="19"/>
-      <c r="G312" s="19"/>
-      <c r="H312" s="19"/>
-      <c r="I312" s="6"/>
-      <c r="J312" s="55"/>
+      <c r="A312" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B312" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C312" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D312" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E312" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F312" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G312" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="H312" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I312" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J312" s="55">
+        <v>10</v>
+      </c>
       <c r="K312" s="20"/>
       <c r="L312" s="20"/>
       <c r="M312" s="20"/>
@@ -42858,45 +43762,67 @@
       </c>
       <c r="AE312" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF312" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG312" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH312" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI312" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ312" s="5">
         <v>0.18</v>
       </c>
       <c r="AK312" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL312" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP312" s="12"/>
     </row>
     <row r="313" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A313" s="17"/>
-      <c r="C313" s="18"/>
-      <c r="E313" s="6"/>
-      <c r="F313" s="19"/>
-      <c r="G313" s="19"/>
-      <c r="H313" s="19"/>
-      <c r="I313" s="6"/>
-      <c r="J313" s="55"/>
+      <c r="A313" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B313" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C313" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D313" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E313" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F313" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G313" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="H313" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I313" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J313" s="55">
+        <v>10</v>
+      </c>
       <c r="K313" s="20"/>
       <c r="L313" s="20"/>
       <c r="M313" s="20"/>
@@ -42955,45 +43881,67 @@
       </c>
       <c r="AE313" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF313" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG313" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH313" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI313" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ313" s="5">
         <v>0.18</v>
       </c>
       <c r="AK313" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL313" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP313" s="12"/>
     </row>
     <row r="314" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A314" s="17"/>
-      <c r="C314" s="18"/>
-      <c r="E314" s="6"/>
-      <c r="F314" s="19"/>
-      <c r="G314" s="19"/>
-      <c r="H314" s="19"/>
-      <c r="I314" s="6"/>
-      <c r="J314" s="55"/>
+      <c r="A314" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B314" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C314" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D314" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E314" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F314" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G314" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="H314" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I314" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J314" s="55">
+        <v>10</v>
+      </c>
       <c r="K314" s="18"/>
       <c r="L314" s="18"/>
       <c r="M314" s="18"/>
@@ -43001,12 +43949,18 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O314" s="18"/>
-      <c r="P314" s="18"/>
-      <c r="Q314" s="18"/>
+      <c r="O314" s="18">
+        <v>15</v>
+      </c>
+      <c r="P314" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q314" s="18">
+        <v>15</v>
+      </c>
       <c r="R314" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S314" s="18"/>
       <c r="T314" s="18">
@@ -43027,19 +43981,19 @@
       </c>
       <c r="X314" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y314" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z314" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA314" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB314" s="8">
         <v>39.270000000000003</v>
@@ -43052,44 +44006,64 @@
       </c>
       <c r="AE314" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF314" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG314" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH314" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI314" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ314" s="5">
         <v>0.18</v>
       </c>
       <c r="AK314" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL314" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP314" s="12"/>
     </row>
     <row r="315" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A315" s="17"/>
-      <c r="C315" s="18"/>
-      <c r="E315" s="6"/>
-      <c r="F315" s="19"/>
-      <c r="G315" s="19"/>
-      <c r="H315" s="19"/>
-      <c r="I315" s="6"/>
+      <c r="A315" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B315" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C315" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D315" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E315" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F315" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G315" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="H315" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I315" s="6" t="s">
+        <v>294</v>
+      </c>
       <c r="J315" s="55"/>
       <c r="K315" s="18"/>
       <c r="L315" s="18"/>
@@ -43098,12 +44072,18 @@
         <f t="shared" si="121"/>
         <v>0</v>
       </c>
-      <c r="O315" s="20"/>
-      <c r="P315" s="20"/>
-      <c r="Q315" s="20"/>
+      <c r="O315" s="20">
+        <v>40</v>
+      </c>
+      <c r="P315" s="20">
+        <v>20</v>
+      </c>
+      <c r="Q315" s="20">
+        <v>40</v>
+      </c>
       <c r="R315" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S315" s="18"/>
       <c r="T315" s="18">
@@ -43124,19 +44104,19 @@
       </c>
       <c r="X315" s="18">
         <f t="shared" si="125"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y315" s="18">
         <f t="shared" si="126"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z315" s="18">
         <f t="shared" si="127"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA315" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB315" s="8">
         <v>39.270000000000003</v>
@@ -43180,14 +44160,36 @@
       <c r="AP315" s="12"/>
     </row>
     <row r="316" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A316" s="17"/>
-      <c r="C316" s="18"/>
-      <c r="E316" s="6"/>
-      <c r="F316" s="19"/>
-      <c r="G316" s="19"/>
-      <c r="H316" s="19"/>
-      <c r="I316" s="6"/>
-      <c r="J316" s="55"/>
+      <c r="A316" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B316" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C316" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D316" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E316" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F316" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G316" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="H316" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I316" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J316" s="55">
+        <v>10</v>
+      </c>
       <c r="K316" s="20"/>
       <c r="L316" s="20"/>
       <c r="M316" s="20"/>
@@ -43246,45 +44248,67 @@
       </c>
       <c r="AE316" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF316" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG316" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH316" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI316" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ316" s="5">
         <v>0.18</v>
       </c>
       <c r="AK316" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL316" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP316" s="12"/>
     </row>
     <row r="317" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A317" s="17"/>
-      <c r="C317" s="18"/>
-      <c r="E317" s="6"/>
-      <c r="F317" s="19"/>
-      <c r="G317" s="19"/>
-      <c r="H317" s="19"/>
-      <c r="I317" s="6"/>
-      <c r="J317" s="55"/>
+      <c r="A317" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B317" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C317" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D317" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E317" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F317" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G317" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="H317" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I317" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J317" s="55">
+        <v>10</v>
+      </c>
       <c r="K317" s="18"/>
       <c r="L317" s="18"/>
       <c r="M317" s="18"/>
@@ -43343,44 +44367,64 @@
       </c>
       <c r="AE317" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>392.70000000000005</v>
       </c>
       <c r="AF317" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG317" s="10">
         <f t="shared" si="128"/>
-        <v>0</v>
+        <v>25.525500000000005</v>
       </c>
       <c r="AH317" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI317" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>367.17450000000002</v>
       </c>
       <c r="AJ317" s="5">
         <v>0.18</v>
       </c>
       <c r="AK317" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>66.091409999999996</v>
       </c>
       <c r="AL317" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>433.26591000000002</v>
       </c>
       <c r="AP317" s="12"/>
     </row>
     <row r="318" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A318" s="17"/>
-      <c r="C318" s="18"/>
-      <c r="E318" s="6"/>
-      <c r="F318" s="19"/>
-      <c r="G318" s="19"/>
-      <c r="H318" s="19"/>
-      <c r="I318" s="6"/>
+      <c r="A318" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B318" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C318" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D318" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E318" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F318" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G318" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="H318" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I318" s="6" t="s">
+        <v>467</v>
+      </c>
       <c r="J318" s="55"/>
       <c r="K318" s="18"/>
       <c r="L318" s="18"/>
@@ -43391,10 +44435,12 @@
       </c>
       <c r="O318" s="20"/>
       <c r="P318" s="20"/>
-      <c r="Q318" s="20"/>
+      <c r="Q318" s="20">
+        <v>40</v>
+      </c>
       <c r="R318" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S318" s="18"/>
       <c r="T318" s="18">
@@ -43423,11 +44469,11 @@
       </c>
       <c r="Z318" s="18">
         <f t="shared" ref="Z318:Z369" si="141">Q318/10</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA318" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB318" s="8">
         <v>39.270000000000003</v>
@@ -43471,36 +44517,66 @@
       <c r="AP318" s="12"/>
     </row>
     <row r="319" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A319" s="17"/>
-      <c r="C319" s="18"/>
-      <c r="E319" s="6"/>
-      <c r="F319" s="19"/>
-      <c r="G319" s="19"/>
-      <c r="H319" s="19"/>
-      <c r="I319" s="6"/>
+      <c r="A319" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B319" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C319" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D319" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E319" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F319" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G319" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H319" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I319" s="6" t="s">
+        <v>468</v>
+      </c>
       <c r="J319" s="55"/>
-      <c r="K319" s="20"/>
-      <c r="L319" s="20"/>
+      <c r="K319" s="20">
+        <v>40</v>
+      </c>
+      <c r="L319" s="20">
+        <v>40</v>
+      </c>
       <c r="M319" s="20"/>
       <c r="N319" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O319" s="18"/>
-      <c r="P319" s="18"/>
-      <c r="Q319" s="20"/>
+        <v>80</v>
+      </c>
+      <c r="O319" s="18">
+        <v>40</v>
+      </c>
+      <c r="P319" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q319" s="20">
+        <v>40</v>
+      </c>
       <c r="R319" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S319" s="18"/>
       <c r="T319" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U319" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V319" s="18">
         <f t="shared" si="138"/>
@@ -43508,23 +44584,23 @@
       </c>
       <c r="W319" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X319" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y319" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z319" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA319" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB319" s="8">
         <v>39.270000000000003</v>
@@ -43537,14 +44613,14 @@
       </c>
       <c r="AE319" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF319" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG319" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH319" s="64">
         <f t="shared" si="132"/>
@@ -43552,52 +44628,82 @@
       </c>
       <c r="AI319" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ319" s="5">
         <v>0.18</v>
       </c>
       <c r="AK319" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL319" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP319" s="12"/>
     </row>
     <row r="320" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A320" s="17"/>
-      <c r="C320" s="18"/>
-      <c r="E320" s="6"/>
-      <c r="F320" s="19"/>
-      <c r="G320" s="19"/>
-      <c r="H320" s="19"/>
-      <c r="I320" s="6"/>
+      <c r="A320" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B320" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C320" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D320" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E320" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F320" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G320" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H320" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I320" s="6" t="s">
+        <v>469</v>
+      </c>
       <c r="J320" s="55"/>
-      <c r="K320" s="20"/>
-      <c r="L320" s="20"/>
+      <c r="K320" s="20">
+        <v>80</v>
+      </c>
+      <c r="L320" s="20">
+        <v>80</v>
+      </c>
       <c r="M320" s="20"/>
       <c r="N320" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O320" s="18"/>
-      <c r="P320" s="18"/>
-      <c r="Q320" s="18"/>
+        <v>160</v>
+      </c>
+      <c r="O320" s="18">
+        <v>80</v>
+      </c>
+      <c r="P320" s="18">
+        <v>80</v>
+      </c>
+      <c r="Q320" s="18">
+        <v>80</v>
+      </c>
       <c r="R320" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S320" s="18"/>
       <c r="T320" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U320" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V320" s="18">
         <f t="shared" si="138"/>
@@ -43605,23 +44711,23 @@
       </c>
       <c r="W320" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X320" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y320" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z320" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA320" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB320" s="8">
         <v>39.270000000000003</v>
@@ -43634,14 +44740,14 @@
       </c>
       <c r="AE320" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>8394</v>
       </c>
       <c r="AF320" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG320" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>545.61</v>
       </c>
       <c r="AH320" s="64">
         <f t="shared" si="132"/>
@@ -43649,52 +44755,82 @@
       </c>
       <c r="AI320" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>7848.39</v>
       </c>
       <c r="AJ320" s="5">
         <v>0.18</v>
       </c>
       <c r="AK320" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1412.7102</v>
       </c>
       <c r="AL320" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>9261.1002000000008</v>
       </c>
       <c r="AP320" s="12"/>
     </row>
     <row r="321" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A321" s="17"/>
-      <c r="C321" s="18"/>
-      <c r="E321" s="6"/>
-      <c r="F321" s="19"/>
-      <c r="G321" s="19"/>
-      <c r="H321" s="19"/>
-      <c r="I321" s="6"/>
+      <c r="A321" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B321" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C321" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D321" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E321" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F321" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G321" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H321" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I321" s="6" t="s">
+        <v>470</v>
+      </c>
       <c r="J321" s="55"/>
-      <c r="K321" s="18"/>
-      <c r="L321" s="18"/>
+      <c r="K321" s="18">
+        <v>40</v>
+      </c>
+      <c r="L321" s="18">
+        <v>40</v>
+      </c>
       <c r="M321" s="18"/>
       <c r="N321" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O321" s="18"/>
-      <c r="P321" s="18"/>
-      <c r="Q321" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O321" s="18">
+        <v>40</v>
+      </c>
+      <c r="P321" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q321" s="18">
+        <v>40</v>
+      </c>
       <c r="R321" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S321" s="18"/>
       <c r="T321" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U321" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V321" s="18">
         <f t="shared" si="138"/>
@@ -43702,23 +44838,23 @@
       </c>
       <c r="W321" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X321" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y321" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z321" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA321" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB321" s="8">
         <v>39.270000000000003</v>
@@ -43731,14 +44867,14 @@
       </c>
       <c r="AE321" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF321" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG321" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH321" s="64">
         <f t="shared" si="132"/>
@@ -43746,52 +44882,82 @@
       </c>
       <c r="AI321" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ321" s="5">
         <v>0.18</v>
       </c>
       <c r="AK321" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL321" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP321" s="12"/>
     </row>
     <row r="322" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A322" s="17"/>
-      <c r="C322" s="18"/>
-      <c r="E322" s="6"/>
-      <c r="F322" s="19"/>
-      <c r="G322" s="19"/>
-      <c r="H322" s="19"/>
-      <c r="I322" s="6"/>
+      <c r="A322" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B322" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C322" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D322" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E322" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F322" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G322" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H322" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I322" s="6" t="s">
+        <v>471</v>
+      </c>
       <c r="J322" s="55"/>
-      <c r="K322" s="20"/>
-      <c r="L322" s="20"/>
+      <c r="K322" s="20">
+        <v>80</v>
+      </c>
+      <c r="L322" s="20">
+        <v>80</v>
+      </c>
       <c r="M322" s="20"/>
       <c r="N322" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O322" s="18"/>
-      <c r="P322" s="18"/>
-      <c r="Q322" s="18"/>
+        <v>160</v>
+      </c>
+      <c r="O322" s="18">
+        <v>80</v>
+      </c>
+      <c r="P322" s="18">
+        <v>80</v>
+      </c>
+      <c r="Q322" s="18">
+        <v>80</v>
+      </c>
       <c r="R322" s="8">
         <f t="shared" si="120"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S322" s="18"/>
       <c r="T322" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U322" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V322" s="18">
         <f t="shared" si="138"/>
@@ -43799,23 +44965,23 @@
       </c>
       <c r="W322" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X322" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y322" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z322" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA322" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB322" s="8">
         <v>39.270000000000003</v>
@@ -43828,14 +44994,14 @@
       </c>
       <c r="AE322" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>8394</v>
       </c>
       <c r="AF322" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG322" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>545.61</v>
       </c>
       <c r="AH322" s="64">
         <f t="shared" si="132"/>
@@ -43843,52 +45009,82 @@
       </c>
       <c r="AI322" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>7848.39</v>
       </c>
       <c r="AJ322" s="5">
         <v>0.18</v>
       </c>
       <c r="AK322" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1412.7102</v>
       </c>
       <c r="AL322" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>9261.1002000000008</v>
       </c>
       <c r="AP322" s="12"/>
     </row>
     <row r="323" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A323" s="17"/>
-      <c r="C323" s="18"/>
-      <c r="E323" s="6"/>
-      <c r="F323" s="19"/>
-      <c r="G323" s="19"/>
-      <c r="H323" s="19"/>
-      <c r="I323" s="6"/>
+      <c r="A323" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B323" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C323" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D323" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E323" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F323" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G323" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H323" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I323" s="6" t="s">
+        <v>472</v>
+      </c>
       <c r="J323" s="55"/>
-      <c r="K323" s="20"/>
-      <c r="L323" s="20"/>
+      <c r="K323" s="20">
+        <v>40</v>
+      </c>
+      <c r="L323" s="20">
+        <v>40</v>
+      </c>
       <c r="M323" s="20"/>
       <c r="N323" s="8">
         <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="O323" s="18"/>
-      <c r="P323" s="20"/>
-      <c r="Q323" s="20"/>
+        <v>80</v>
+      </c>
+      <c r="O323" s="18">
+        <v>40</v>
+      </c>
+      <c r="P323" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q323" s="20">
+        <v>40</v>
+      </c>
       <c r="R323" s="8">
         <f t="shared" ref="R323:R386" si="143">SUM(O323:Q323)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S323" s="18"/>
       <c r="T323" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U323" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V323" s="18">
         <f t="shared" si="138"/>
@@ -43896,23 +45092,23 @@
       </c>
       <c r="W323" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X323" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y323" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z323" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA323" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB323" s="8">
         <v>39.270000000000003</v>
@@ -43925,14 +45121,14 @@
       </c>
       <c r="AE323" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF323" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG323" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH323" s="64">
         <f t="shared" si="132"/>
@@ -43940,52 +45136,82 @@
       </c>
       <c r="AI323" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ323" s="5">
         <v>0.18</v>
       </c>
       <c r="AK323" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL323" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP323" s="12"/>
     </row>
     <row r="324" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A324" s="17"/>
-      <c r="C324" s="18"/>
-      <c r="E324" s="6"/>
-      <c r="F324" s="19"/>
-      <c r="G324" s="19"/>
-      <c r="H324" s="19"/>
-      <c r="I324" s="6"/>
+      <c r="A324" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B324" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C324" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D324" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E324" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F324" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G324" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H324" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I324" s="6" t="s">
+        <v>473</v>
+      </c>
       <c r="J324" s="55"/>
-      <c r="K324" s="20"/>
-      <c r="L324" s="20"/>
+      <c r="K324" s="20">
+        <v>40</v>
+      </c>
+      <c r="L324" s="20">
+        <v>40</v>
+      </c>
       <c r="M324" s="20"/>
       <c r="N324" s="8">
         <f t="shared" ref="N324:N387" si="144">K324+L324+M324</f>
-        <v>0</v>
-      </c>
-      <c r="O324" s="18"/>
-      <c r="P324" s="20"/>
-      <c r="Q324" s="20"/>
+        <v>80</v>
+      </c>
+      <c r="O324" s="18">
+        <v>40</v>
+      </c>
+      <c r="P324" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q324" s="20">
+        <v>40</v>
+      </c>
       <c r="R324" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S324" s="18"/>
       <c r="T324" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U324" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V324" s="18">
         <f t="shared" si="138"/>
@@ -43993,23 +45219,23 @@
       </c>
       <c r="W324" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X324" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y324" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z324" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA324" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB324" s="8">
         <v>39.270000000000003</v>
@@ -44022,14 +45248,14 @@
       </c>
       <c r="AE324" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF324" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG324" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH324" s="64">
         <f t="shared" si="132"/>
@@ -44037,52 +45263,82 @@
       </c>
       <c r="AI324" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ324" s="5">
         <v>0.18</v>
       </c>
       <c r="AK324" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL324" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP324" s="12"/>
     </row>
     <row r="325" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A325" s="17"/>
-      <c r="C325" s="18"/>
-      <c r="E325" s="6"/>
-      <c r="F325" s="19"/>
-      <c r="G325" s="19"/>
-      <c r="H325" s="19"/>
-      <c r="I325" s="6"/>
+      <c r="A325" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B325" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C325" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D325" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E325" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F325" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G325" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H325" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I325" s="6" t="s">
+        <v>474</v>
+      </c>
       <c r="J325" s="55"/>
-      <c r="K325" s="20"/>
-      <c r="L325" s="20"/>
+      <c r="K325" s="20">
+        <v>40</v>
+      </c>
+      <c r="L325" s="20">
+        <v>40</v>
+      </c>
       <c r="M325" s="20"/>
       <c r="N325" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O325" s="18"/>
-      <c r="P325" s="18"/>
-      <c r="Q325" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O325" s="18">
+        <v>40</v>
+      </c>
+      <c r="P325" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q325" s="18">
+        <v>40</v>
+      </c>
       <c r="R325" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S325" s="18"/>
       <c r="T325" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U325" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V325" s="18">
         <f t="shared" si="138"/>
@@ -44090,23 +45346,23 @@
       </c>
       <c r="W325" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X325" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y325" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z325" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA325" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB325" s="8">
         <v>39.270000000000003</v>
@@ -44119,14 +45375,14 @@
       </c>
       <c r="AE325" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF325" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG325" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH325" s="64">
         <f t="shared" si="132"/>
@@ -44134,52 +45390,82 @@
       </c>
       <c r="AI325" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ325" s="5">
         <v>0.18</v>
       </c>
       <c r="AK325" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL325" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP325" s="12"/>
     </row>
     <row r="326" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A326" s="17"/>
-      <c r="C326" s="18"/>
-      <c r="E326" s="6"/>
-      <c r="F326" s="19"/>
-      <c r="G326" s="19"/>
-      <c r="H326" s="19"/>
-      <c r="I326" s="6"/>
+      <c r="A326" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B326" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C326" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D326" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E326" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F326" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G326" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H326" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I326" s="6" t="s">
+        <v>475</v>
+      </c>
       <c r="J326" s="55"/>
-      <c r="K326" s="18"/>
-      <c r="L326" s="18"/>
+      <c r="K326" s="18">
+        <v>40</v>
+      </c>
+      <c r="L326" s="18">
+        <v>40</v>
+      </c>
       <c r="M326" s="18"/>
       <c r="N326" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O326" s="18"/>
-      <c r="P326" s="18"/>
-      <c r="Q326" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O326" s="18">
+        <v>40</v>
+      </c>
+      <c r="P326" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q326" s="18">
+        <v>40</v>
+      </c>
       <c r="R326" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S326" s="18"/>
       <c r="T326" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U326" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V326" s="18">
         <f t="shared" si="138"/>
@@ -44187,23 +45473,23 @@
       </c>
       <c r="W326" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X326" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y326" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z326" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA326" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB326" s="8">
         <v>39.270000000000003</v>
@@ -44216,14 +45502,14 @@
       </c>
       <c r="AE326" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF326" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG326" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH326" s="64">
         <f t="shared" si="132"/>
@@ -44231,52 +45517,82 @@
       </c>
       <c r="AI326" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ326" s="5">
         <v>0.18</v>
       </c>
       <c r="AK326" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL326" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP326" s="12"/>
     </row>
     <row r="327" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A327" s="17"/>
-      <c r="C327" s="18"/>
-      <c r="E327" s="6"/>
-      <c r="F327" s="19"/>
-      <c r="G327" s="19"/>
-      <c r="H327" s="19"/>
-      <c r="I327" s="6"/>
+      <c r="A327" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B327" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C327" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D327" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E327" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F327" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G327" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H327" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I327" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="J327" s="55"/>
-      <c r="K327" s="18"/>
-      <c r="L327" s="18"/>
+      <c r="K327" s="18">
+        <v>40</v>
+      </c>
+      <c r="L327" s="18">
+        <v>40</v>
+      </c>
       <c r="M327" s="18"/>
       <c r="N327" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O327" s="18"/>
-      <c r="P327" s="18"/>
-      <c r="Q327" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O327" s="18">
+        <v>40</v>
+      </c>
+      <c r="P327" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q327" s="18">
+        <v>40</v>
+      </c>
       <c r="R327" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S327" s="18"/>
       <c r="T327" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U327" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V327" s="18">
         <f t="shared" si="138"/>
@@ -44284,23 +45600,23 @@
       </c>
       <c r="W327" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X327" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y327" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z327" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA327" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB327" s="8">
         <v>39.270000000000003</v>
@@ -44313,14 +45629,14 @@
       </c>
       <c r="AE327" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF327" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG327" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH327" s="64">
         <f t="shared" si="132"/>
@@ -44328,52 +45644,82 @@
       </c>
       <c r="AI327" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ327" s="5">
         <v>0.18</v>
       </c>
       <c r="AK327" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL327" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP327" s="12"/>
     </row>
     <row r="328" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A328" s="17"/>
-      <c r="C328" s="18"/>
-      <c r="E328" s="6"/>
-      <c r="F328" s="19"/>
-      <c r="G328" s="19"/>
-      <c r="H328" s="19"/>
-      <c r="I328" s="6"/>
+      <c r="A328" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B328" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C328" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D328" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E328" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F328" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G328" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="H328" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I328" s="6" t="s">
+        <v>477</v>
+      </c>
       <c r="J328" s="55"/>
-      <c r="K328" s="18"/>
-      <c r="L328" s="18"/>
+      <c r="K328" s="18">
+        <v>40</v>
+      </c>
+      <c r="L328" s="18">
+        <v>40</v>
+      </c>
       <c r="M328" s="18"/>
       <c r="N328" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O328" s="18"/>
-      <c r="P328" s="18"/>
-      <c r="Q328" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O328" s="18">
+        <v>40</v>
+      </c>
+      <c r="P328" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q328" s="18">
+        <v>40</v>
+      </c>
       <c r="R328" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S328" s="18"/>
       <c r="T328" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U328" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V328" s="18">
         <f t="shared" si="138"/>
@@ -44381,23 +45727,23 @@
       </c>
       <c r="W328" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X328" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y328" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z328" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA328" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB328" s="8">
         <v>39.270000000000003</v>
@@ -44410,14 +45756,14 @@
       </c>
       <c r="AE328" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF328" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG328" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH328" s="64">
         <f t="shared" si="132"/>
@@ -44425,52 +45771,82 @@
       </c>
       <c r="AI328" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ328" s="5">
         <v>0.18</v>
       </c>
       <c r="AK328" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL328" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP328" s="12"/>
     </row>
     <row r="329" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A329" s="17"/>
-      <c r="C329" s="18"/>
-      <c r="E329" s="6"/>
-      <c r="F329" s="19"/>
-      <c r="G329" s="19"/>
-      <c r="H329" s="19"/>
-      <c r="I329" s="6"/>
+      <c r="A329" s="71">
+        <v>46196</v>
+      </c>
+      <c r="B329" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C329" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D329" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E329" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F329" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G329" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="H329" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I329" s="6" t="s">
+        <v>477</v>
+      </c>
       <c r="J329" s="55"/>
-      <c r="K329" s="18"/>
-      <c r="L329" s="18"/>
+      <c r="K329" s="18">
+        <v>84</v>
+      </c>
+      <c r="L329" s="18">
+        <v>84</v>
+      </c>
       <c r="M329" s="18"/>
       <c r="N329" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O329" s="20"/>
-      <c r="P329" s="20"/>
-      <c r="Q329" s="20"/>
+        <v>168</v>
+      </c>
+      <c r="O329" s="20">
+        <v>168</v>
+      </c>
+      <c r="P329" s="20">
+        <v>126</v>
+      </c>
+      <c r="Q329" s="20">
+        <v>252</v>
+      </c>
       <c r="R329" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>546</v>
       </c>
       <c r="S329" s="18"/>
       <c r="T329" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="U329" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="V329" s="18">
         <f t="shared" si="138"/>
@@ -44478,23 +45854,23 @@
       </c>
       <c r="W329" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="X329" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="Y329" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="Z329" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="AA329" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>54.6</v>
       </c>
       <c r="AB329" s="8">
         <v>39.270000000000003</v>
@@ -44507,14 +45883,14 @@
       </c>
       <c r="AE329" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>8813.6999999999989</v>
       </c>
       <c r="AF329" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG329" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>572.89049999999997</v>
       </c>
       <c r="AH329" s="64">
         <f t="shared" si="132"/>
@@ -44522,52 +45898,84 @@
       </c>
       <c r="AI329" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>8240.8094999999994</v>
       </c>
       <c r="AJ329" s="5">
         <v>0.18</v>
       </c>
       <c r="AK329" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1483.3457099999998</v>
       </c>
       <c r="AL329" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>9724.155209999999</v>
       </c>
       <c r="AP329" s="12"/>
     </row>
     <row r="330" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A330" s="17"/>
-      <c r="C330" s="18"/>
-      <c r="E330" s="6"/>
-      <c r="F330" s="19"/>
-      <c r="G330" s="19"/>
-      <c r="H330" s="19"/>
-      <c r="I330" s="6"/>
-      <c r="J330" s="55"/>
-      <c r="K330" s="18"/>
-      <c r="L330" s="18"/>
+      <c r="A330" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B330" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C330" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D330" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E330" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F330" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G330" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="H330" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I330" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="J330" s="55">
+        <v>80</v>
+      </c>
+      <c r="K330" s="18">
+        <v>80</v>
+      </c>
+      <c r="L330" s="18">
+        <v>80</v>
+      </c>
       <c r="M330" s="18"/>
       <c r="N330" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O330" s="20"/>
-      <c r="P330" s="20"/>
-      <c r="Q330" s="20"/>
+        <v>160</v>
+      </c>
+      <c r="O330" s="20">
+        <v>80</v>
+      </c>
+      <c r="P330" s="20">
+        <v>80</v>
+      </c>
+      <c r="Q330" s="20">
+        <v>80</v>
+      </c>
       <c r="R330" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S330" s="18"/>
       <c r="T330" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U330" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V330" s="18">
         <f t="shared" si="138"/>
@@ -44575,23 +45983,23 @@
       </c>
       <c r="W330" s="8">
         <f t="shared" si="129"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X330" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y330" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z330" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA330" s="8">
         <f t="shared" si="130"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB330" s="8">
         <v>39.270000000000003</v>
@@ -44604,67 +46012,97 @@
       </c>
       <c r="AE330" s="9">
         <f t="shared" si="131"/>
-        <v>0</v>
+        <v>11535.6</v>
       </c>
       <c r="AF330" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG330" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>749.81400000000008</v>
       </c>
       <c r="AH330" s="64">
         <f t="shared" si="132"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI330" s="9">
         <f t="shared" si="133"/>
-        <v>0</v>
+        <v>10785.786</v>
       </c>
       <c r="AJ330" s="5">
         <v>0.18</v>
       </c>
       <c r="AK330" s="11">
         <f t="shared" si="134"/>
-        <v>0</v>
+        <v>1941.44148</v>
       </c>
       <c r="AL330" s="9">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>12727.22748</v>
       </c>
       <c r="AP330" s="12"/>
     </row>
     <row r="331" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A331" s="17"/>
-      <c r="C331" s="18"/>
-      <c r="E331" s="6"/>
-      <c r="F331" s="19"/>
-      <c r="G331" s="19"/>
-      <c r="H331" s="19"/>
-      <c r="I331" s="6"/>
+      <c r="A331" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B331" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C331" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D331" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E331" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F331" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G331" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="H331" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I331" s="6" t="s">
+        <v>485</v>
+      </c>
       <c r="J331" s="55"/>
-      <c r="K331" s="18"/>
-      <c r="L331" s="18"/>
+      <c r="K331" s="18">
+        <v>80</v>
+      </c>
+      <c r="L331" s="18">
+        <v>80</v>
+      </c>
       <c r="M331" s="18"/>
       <c r="N331" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O331" s="20"/>
-      <c r="P331" s="20"/>
-      <c r="Q331" s="20"/>
+        <v>160</v>
+      </c>
+      <c r="O331" s="20">
+        <v>80</v>
+      </c>
+      <c r="P331" s="20">
+        <v>80</v>
+      </c>
+      <c r="Q331" s="20">
+        <v>80</v>
+      </c>
       <c r="R331" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S331" s="18"/>
       <c r="T331" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U331" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V331" s="18">
         <f t="shared" si="138"/>
@@ -44672,23 +46110,23 @@
       </c>
       <c r="W331" s="8">
         <f t="shared" ref="W331:W394" si="145">N331/10</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X331" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y331" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z331" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA331" s="8">
         <f t="shared" ref="AA331:AA394" si="146">R331/10</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB331" s="8">
         <v>39.270000000000003</v>
@@ -44701,14 +46139,14 @@
       </c>
       <c r="AE331" s="9">
         <f t="shared" ref="AE331:AE394" si="147">(J331*AB331)+(N331*AC331)+(AD331*S331)</f>
-        <v>0</v>
+        <v>8394</v>
       </c>
       <c r="AF331" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG331" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>545.61</v>
       </c>
       <c r="AH331" s="64">
         <f t="shared" ref="AH331:AH394" si="148">(AB331*J331)*$AH$1</f>
@@ -44716,52 +46154,82 @@
       </c>
       <c r="AI331" s="9">
         <f t="shared" ref="AI331:AI394" si="149">AE331-AG331</f>
-        <v>0</v>
+        <v>7848.39</v>
       </c>
       <c r="AJ331" s="5">
         <v>0.18</v>
       </c>
       <c r="AK331" s="11">
         <f t="shared" ref="AK331:AK394" si="150">AI331*AJ331</f>
-        <v>0</v>
+        <v>1412.7102</v>
       </c>
       <c r="AL331" s="9">
         <f t="shared" ref="AL331:AL394" si="151">AI331+AK331</f>
-        <v>0</v>
+        <v>9261.1002000000008</v>
       </c>
       <c r="AP331" s="12"/>
     </row>
     <row r="332" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A332" s="17"/>
-      <c r="C332" s="18"/>
-      <c r="E332" s="6"/>
-      <c r="F332" s="19"/>
-      <c r="G332" s="19"/>
-      <c r="H332" s="19"/>
-      <c r="I332" s="6"/>
+      <c r="A332" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B332" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C332" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D332" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E332" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F332" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G332" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="H332" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I332" s="6" t="s">
+        <v>486</v>
+      </c>
       <c r="J332" s="55"/>
-      <c r="K332" s="20"/>
-      <c r="L332" s="20"/>
+      <c r="K332" s="20">
+        <v>80</v>
+      </c>
+      <c r="L332" s="20">
+        <v>80</v>
+      </c>
       <c r="M332" s="18"/>
       <c r="N332" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O332" s="20"/>
-      <c r="P332" s="20"/>
-      <c r="Q332" s="18"/>
+        <v>160</v>
+      </c>
+      <c r="O332" s="20">
+        <v>80</v>
+      </c>
+      <c r="P332" s="20">
+        <v>80</v>
+      </c>
+      <c r="Q332" s="18">
+        <v>80</v>
+      </c>
       <c r="R332" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S332" s="18"/>
       <c r="T332" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U332" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V332" s="18">
         <f t="shared" si="138"/>
@@ -44769,23 +46237,23 @@
       </c>
       <c r="W332" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X332" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y332" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z332" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA332" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB332" s="8">
         <v>39.270000000000003</v>
@@ -44798,14 +46266,14 @@
       </c>
       <c r="AE332" s="9">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>8394</v>
       </c>
       <c r="AF332" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG332" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>545.61</v>
       </c>
       <c r="AH332" s="64">
         <f t="shared" si="148"/>
@@ -44813,29 +46281,49 @@
       </c>
       <c r="AI332" s="9">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>7848.39</v>
       </c>
       <c r="AJ332" s="5">
         <v>0.18</v>
       </c>
       <c r="AK332" s="11">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1412.7102</v>
       </c>
       <c r="AL332" s="9">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>9261.1002000000008</v>
       </c>
       <c r="AP332" s="12"/>
     </row>
     <row r="333" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A333" s="17"/>
-      <c r="C333" s="18"/>
-      <c r="E333" s="6"/>
-      <c r="F333" s="19"/>
-      <c r="G333" s="19"/>
-      <c r="H333" s="19"/>
-      <c r="I333" s="6"/>
+      <c r="A333" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B333" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C333" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D333" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E333" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F333" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G333" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="H333" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I333" s="6" t="s">
+        <v>487</v>
+      </c>
       <c r="J333" s="55"/>
       <c r="K333" s="18"/>
       <c r="L333" s="18"/>
@@ -44844,12 +46332,18 @@
         <f t="shared" si="144"/>
         <v>0</v>
       </c>
-      <c r="O333" s="18"/>
-      <c r="P333" s="18"/>
-      <c r="Q333" s="18"/>
+      <c r="O333" s="18">
+        <v>40</v>
+      </c>
+      <c r="P333" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q333" s="18">
+        <v>40</v>
+      </c>
       <c r="R333" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S333" s="18"/>
       <c r="T333" s="18">
@@ -44870,19 +46364,19 @@
       </c>
       <c r="X333" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y333" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z333" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA333" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB333" s="8">
         <v>39.270000000000003</v>
@@ -44926,36 +46420,66 @@
       <c r="AP333" s="12"/>
     </row>
     <row r="334" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A334" s="17"/>
-      <c r="C334" s="18"/>
-      <c r="E334" s="6"/>
-      <c r="F334" s="19"/>
-      <c r="G334" s="19"/>
-      <c r="H334" s="19"/>
-      <c r="I334" s="6"/>
+      <c r="A334" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B334" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C334" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D334" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E334" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F334" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G334" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="H334" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I334" s="6" t="s">
+        <v>488</v>
+      </c>
       <c r="J334" s="55"/>
-      <c r="K334" s="18"/>
-      <c r="L334" s="18"/>
+      <c r="K334" s="18">
+        <v>80</v>
+      </c>
+      <c r="L334" s="18">
+        <v>80</v>
+      </c>
       <c r="M334" s="18"/>
       <c r="N334" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O334" s="18"/>
-      <c r="P334" s="18"/>
-      <c r="Q334" s="18"/>
+        <v>160</v>
+      </c>
+      <c r="O334" s="18">
+        <v>80</v>
+      </c>
+      <c r="P334" s="18">
+        <v>80</v>
+      </c>
+      <c r="Q334" s="18">
+        <v>80</v>
+      </c>
       <c r="R334" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S334" s="18"/>
       <c r="T334" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U334" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V334" s="18">
         <f t="shared" si="138"/>
@@ -44963,23 +46487,23 @@
       </c>
       <c r="W334" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X334" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y334" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z334" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA334" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB334" s="8">
         <v>39.270000000000003</v>
@@ -44992,14 +46516,14 @@
       </c>
       <c r="AE334" s="9">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>8394</v>
       </c>
       <c r="AF334" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG334" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>545.61</v>
       </c>
       <c r="AH334" s="64">
         <f t="shared" si="148"/>
@@ -45007,52 +46531,82 @@
       </c>
       <c r="AI334" s="9">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>7848.39</v>
       </c>
       <c r="AJ334" s="5">
         <v>0.18</v>
       </c>
       <c r="AK334" s="11">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1412.7102</v>
       </c>
       <c r="AL334" s="9">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>9261.1002000000008</v>
       </c>
       <c r="AP334" s="12"/>
     </row>
     <row r="335" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A335" s="17"/>
-      <c r="C335" s="18"/>
-      <c r="E335" s="6"/>
-      <c r="F335" s="19"/>
-      <c r="G335" s="19"/>
-      <c r="H335" s="19"/>
-      <c r="I335" s="6"/>
+      <c r="A335" s="71">
+        <v>46197</v>
+      </c>
+      <c r="B335" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C335" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D335" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E335" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F335" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G335" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="H335" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I335" s="6" t="s">
+        <v>489</v>
+      </c>
       <c r="J335" s="55"/>
-      <c r="K335" s="20"/>
-      <c r="L335" s="20"/>
+      <c r="K335" s="20">
+        <v>80</v>
+      </c>
+      <c r="L335" s="20">
+        <v>80</v>
+      </c>
       <c r="M335" s="20"/>
       <c r="N335" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="O335" s="18"/>
-      <c r="P335" s="18"/>
-      <c r="Q335" s="18"/>
+        <v>160</v>
+      </c>
+      <c r="O335" s="18">
+        <v>80</v>
+      </c>
+      <c r="P335" s="18">
+        <v>120</v>
+      </c>
+      <c r="Q335" s="18">
+        <v>80</v>
+      </c>
       <c r="R335" s="8">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="S335" s="18"/>
       <c r="T335" s="18">
         <f t="shared" si="136"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U335" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V335" s="18">
         <f t="shared" si="138"/>
@@ -45060,23 +46614,23 @@
       </c>
       <c r="W335" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X335" s="18">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y335" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z335" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA335" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB335" s="8">
         <v>39.270000000000003</v>
@@ -45089,14 +46643,14 @@
       </c>
       <c r="AE335" s="9">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>8394</v>
       </c>
       <c r="AF335" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG335" s="10">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>545.61</v>
       </c>
       <c r="AH335" s="64">
         <f t="shared" si="148"/>
@@ -45104,18 +46658,18 @@
       </c>
       <c r="AI335" s="9">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>7848.39</v>
       </c>
       <c r="AJ335" s="5">
         <v>0.18</v>
       </c>
       <c r="AK335" s="11">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1412.7102</v>
       </c>
       <c r="AL335" s="9">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>9261.1002000000008</v>
       </c>
       <c r="AP335" s="12"/>
     </row>
@@ -53762,103 +55316,103 @@
       <c r="I425" s="6"/>
       <c r="J425" s="6">
         <f t="shared" ref="J425:AA425" si="175">SUM(J3:J424)</f>
-        <v>5969</v>
+        <v>6491</v>
       </c>
       <c r="K425" s="6">
         <f t="shared" si="175"/>
-        <v>14765</v>
+        <v>16138</v>
       </c>
       <c r="L425" s="6">
         <f t="shared" si="175"/>
-        <v>13949</v>
+        <v>15262</v>
       </c>
       <c r="M425" s="6">
         <f t="shared" si="175"/>
-        <v>17321</v>
+        <v>17523</v>
       </c>
       <c r="N425" s="6">
         <f t="shared" si="175"/>
-        <v>46035</v>
+        <v>48923</v>
       </c>
       <c r="O425" s="6">
         <f t="shared" si="175"/>
-        <v>21600</v>
+        <v>23173</v>
       </c>
       <c r="P425" s="6">
         <f t="shared" si="175"/>
-        <v>18284</v>
+        <v>19778</v>
       </c>
       <c r="Q425" s="6">
         <f t="shared" si="175"/>
-        <v>25900</v>
+        <v>27639</v>
       </c>
       <c r="R425" s="6">
         <f>SUM(R3:R424)</f>
-        <v>65784</v>
+        <v>70590</v>
       </c>
       <c r="S425" s="6">
         <f>SUM(S3:S424)</f>
-        <v>117788</v>
+        <v>118428</v>
       </c>
       <c r="T425" s="6">
         <f t="shared" si="175"/>
-        <v>1476.1</v>
+        <v>1613.4</v>
       </c>
       <c r="U425" s="6">
         <f t="shared" si="175"/>
-        <v>1394.6000000000001</v>
+        <v>1525.9000000000003</v>
       </c>
       <c r="V425" s="6">
         <f t="shared" si="175"/>
-        <v>1731.9499999999996</v>
+        <v>1752.1499999999996</v>
       </c>
       <c r="W425" s="6">
         <f t="shared" si="175"/>
-        <v>4602.6499999999996</v>
+        <v>4891.45</v>
       </c>
       <c r="X425" s="6">
         <f t="shared" si="175"/>
-        <v>2159.9999999999995</v>
+        <v>2317.3000000000002</v>
       </c>
       <c r="Y425" s="6">
         <f t="shared" si="175"/>
-        <v>1828.3999999999999</v>
+        <v>1977.8</v>
       </c>
       <c r="Z425" s="6">
         <f t="shared" si="175"/>
-        <v>2590</v>
+        <v>2763.8999999999996</v>
       </c>
       <c r="AA425" s="6">
         <f t="shared" si="175"/>
-        <v>6578.3999999999987</v>
+        <v>7058.9999999999991</v>
       </c>
       <c r="AB425" s="6"/>
       <c r="AC425" s="6"/>
       <c r="AD425" s="6"/>
-      <c r="AE425" s="6">
+      <c r="AE425" s="6" t="e">
         <f>SUM(AE3:AE424)</f>
-        <v>11205634.137499981</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AF425" s="7"/>
-      <c r="AG425" s="6">
+      <c r="AG425" s="6" t="e">
         <f>SUM(AG3:AG424)</f>
-        <v>794498.53991250135</v>
-      </c>
-      <c r="AH425" s="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AH425" s="6" t="e">
         <f>SUM(AH3:AH424)</f>
-        <v>8204.0920499999975</v>
-      </c>
-      <c r="AI425" s="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AI425" s="6" t="e">
         <f>SUM(AI3:AI424)</f>
-        <v>10411066.875087487</v>
-      </c>
-      <c r="AK425" s="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AK425" s="6" t="e">
         <f>SUM(AK3:AK424)</f>
-        <v>1873992.0375157497</v>
-      </c>
-      <c r="AL425" s="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AL425" s="6" t="e">
         <f>SUM(AL3:AL424)</f>
-        <v>12285058.912603237</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AP425" s="12"/>
     </row>
@@ -53935,75 +55489,75 @@
       </c>
       <c r="J429" s="61">
         <f t="shared" ref="J429:AF429" si="176">+J425/40</f>
-        <v>149.22499999999999</v>
+        <v>162.27500000000001</v>
       </c>
       <c r="K429" s="62">
         <f t="shared" si="176"/>
-        <v>369.125</v>
+        <v>403.45</v>
       </c>
       <c r="L429" s="62">
         <f t="shared" si="176"/>
-        <v>348.72500000000002</v>
+        <v>381.55</v>
       </c>
       <c r="M429" s="62">
         <f t="shared" si="176"/>
-        <v>433.02499999999998</v>
+        <v>438.07499999999999</v>
       </c>
       <c r="N429" s="61">
         <f t="shared" si="176"/>
-        <v>1150.875</v>
+        <v>1223.075</v>
       </c>
       <c r="O429" s="62">
         <f t="shared" si="176"/>
-        <v>540</v>
+        <v>579.32500000000005</v>
       </c>
       <c r="P429" s="62">
         <f t="shared" si="176"/>
-        <v>457.1</v>
+        <v>494.45</v>
       </c>
       <c r="Q429" s="62">
         <f t="shared" si="176"/>
-        <v>647.5</v>
+        <v>690.97500000000002</v>
       </c>
       <c r="R429" s="61">
         <f t="shared" si="176"/>
-        <v>1644.6</v>
+        <v>1764.75</v>
       </c>
       <c r="S429" s="80">
         <f t="shared" si="176"/>
-        <v>2944.7</v>
+        <v>2960.7</v>
       </c>
       <c r="T429" s="80">
         <f t="shared" si="176"/>
-        <v>36.902499999999996</v>
+        <v>40.335000000000001</v>
       </c>
       <c r="U429" s="80">
         <f t="shared" si="176"/>
-        <v>34.865000000000002</v>
+        <v>38.147500000000008</v>
       </c>
       <c r="V429" s="80">
         <f t="shared" si="176"/>
-        <v>43.298749999999991</v>
+        <v>43.803749999999994</v>
       </c>
       <c r="W429" s="80">
         <f t="shared" si="176"/>
-        <v>115.06625</v>
+        <v>122.28625</v>
       </c>
       <c r="X429" s="80">
         <f t="shared" si="176"/>
-        <v>53.999999999999986</v>
+        <v>57.932500000000005</v>
       </c>
       <c r="Y429" s="80">
         <f t="shared" si="176"/>
-        <v>45.709999999999994</v>
+        <v>49.445</v>
       </c>
       <c r="Z429" s="80">
         <f t="shared" si="176"/>
-        <v>64.75</v>
+        <v>69.097499999999997</v>
       </c>
       <c r="AA429" s="80">
         <f t="shared" si="176"/>
-        <v>164.45999999999998</v>
+        <v>176.47499999999997</v>
       </c>
       <c r="AB429" s="81"/>
       <c r="AC429" s="57">
@@ -54014,9 +55568,9 @@
         <f t="shared" si="176"/>
         <v>0</v>
       </c>
-      <c r="AE429" s="57">
+      <c r="AE429" s="57" t="e">
         <f t="shared" si="176"/>
-        <v>280140.85343749949</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AF429" s="57">
         <f t="shared" si="176"/>
@@ -54036,7 +55590,7 @@
     <row r="431" spans="1:42" x14ac:dyDescent="0.35">
       <c r="S431" s="79">
         <f>S429+W429+AA429</f>
-        <v>3224.2262499999997</v>
+        <v>3259.4612499999998</v>
       </c>
       <c r="X431" t="s">
         <v>50</v>
@@ -54058,13 +55612,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -54077,14 +55632,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -54110,22 +55664,22 @@
   <sheetData>
     <row r="3" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="4:8" ht="22.5" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="D4" s="112" t="s">
+      <c r="D4" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="115"/>
     </row>
     <row r="5" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D5" s="22" t="s">
         <v>355</v>
       </c>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
     </row>
     <row r="6" spans="4:8" x14ac:dyDescent="0.35">
       <c r="D6" s="23" t="s">
@@ -54156,11 +55710,11 @@
       </c>
       <c r="G7" s="29">
         <f>'STT Report'!Q429+'STT Report'!Z429</f>
-        <v>712.25</v>
+        <v>760.07249999999999</v>
       </c>
       <c r="H7" s="30">
         <f>E7+F7-G7</f>
-        <v>216.85000000000002</v>
+        <v>169.02750000000003</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -54175,11 +55729,11 @@
       </c>
       <c r="G8" s="29">
         <f>'STT Report'!P429+'STT Report'!Y429</f>
-        <v>502.81</v>
+        <v>543.89499999999998</v>
       </c>
       <c r="H8" s="30">
         <f>E8+F8-G8</f>
-        <v>176.29000000000002</v>
+        <v>135.20500000000004</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -54194,11 +55748,11 @@
       </c>
       <c r="G9" s="29">
         <f>'STT Report'!O429+'STT Report'!X429</f>
-        <v>594</v>
+        <v>637.25750000000005</v>
       </c>
       <c r="H9" s="30">
         <f>E9+F9-G9</f>
-        <v>274.29999999999995</v>
+        <v>231.0424999999999</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -54215,11 +55769,11 @@
       </c>
       <c r="G10" s="35">
         <f>SUM(G7:G9)</f>
-        <v>1809.06</v>
+        <v>1941.2249999999999</v>
       </c>
       <c r="H10" s="36">
         <f>SUM(H7:H9)</f>
-        <v>667.44</v>
+        <v>535.27499999999998</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -54234,11 +55788,11 @@
       </c>
       <c r="G11" s="58">
         <f>'STT Report'!J429</f>
-        <v>149.22499999999999</v>
+        <v>162.27500000000001</v>
       </c>
       <c r="H11" s="30">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>1725.6750000000002</v>
+        <v>1712.625</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -54275,11 +55829,11 @@
       </c>
       <c r="G14" s="33">
         <f>SUM(G11:G13)</f>
-        <v>149.22499999999999</v>
+        <v>162.27500000000001</v>
       </c>
       <c r="H14" s="36">
         <f>SUM(H11:H13)</f>
-        <v>1725.6750000000002</v>
+        <v>1712.625</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -54294,11 +55848,11 @@
       </c>
       <c r="G15" s="29">
         <f>'STT Report'!M429+'STT Report'!V429</f>
-        <v>476.32374999999996</v>
+        <v>481.87874999999997</v>
       </c>
       <c r="H15" s="30">
         <f>E15+F15-G15</f>
-        <v>-91.223749999999939</v>
+        <v>-96.778749999999945</v>
       </c>
     </row>
     <row r="16" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -54313,11 +55867,11 @@
       </c>
       <c r="G16" s="29">
         <f>'STT Report'!L429+'STT Report'!U429</f>
-        <v>383.59000000000003</v>
+        <v>419.69749999999999</v>
       </c>
       <c r="H16" s="30">
         <f>E16+F16-G16</f>
-        <v>250.40999999999997</v>
+        <v>214.30250000000001</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -54332,11 +55886,11 @@
       </c>
       <c r="G17" s="29">
         <f>'STT Report'!K429+'STT Report'!T429</f>
-        <v>406.02749999999997</v>
+        <v>443.78499999999997</v>
       </c>
       <c r="H17" s="30">
         <f>E17+F17-G17</f>
-        <v>222.67250000000007</v>
+        <v>184.91500000000008</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -54353,11 +55907,11 @@
       </c>
       <c r="G18" s="35">
         <f>SUM(G15:G17)</f>
-        <v>1265.9412499999999</v>
+        <v>1345.3612499999999</v>
       </c>
       <c r="H18" s="36">
         <f>SUM(H15:H17)</f>
-        <v>381.8587500000001</v>
+        <v>302.43875000000014</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -54374,11 +55928,11 @@
       </c>
       <c r="G19" s="38">
         <f>G10+G14+G18</f>
-        <v>3224.2262499999997</v>
+        <v>3448.8612499999999</v>
       </c>
       <c r="H19" s="40">
         <f>H10+H14+H18</f>
-        <v>2774.9737500000001</v>
+        <v>2550.3387500000003</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
@@ -54688,10 +56242,10 @@
       </c>
     </row>
     <row r="31" spans="3:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C31" s="116" t="s">
+      <c r="C31" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="117"/>
+      <c r="D31" s="118"/>
       <c r="E31" s="50">
         <f>SUM(E24:E30)</f>
         <v>8000</v>

--- a/STT Report Elite Marketing (20-06-26) (1).xlsx
+++ b/STT Report Elite Marketing (20-06-26) (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CE711C-DB5A-431B-B56F-DFA52032419A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3ED7C7-AB94-4F99-B336-00F2A18E79DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="554">
   <si>
     <t>Date</t>
   </si>
@@ -1593,6 +1593,105 @@
   <si>
     <t>Lake City</t>
   </si>
+  <si>
+    <t>Madina Bakers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W Mart </t>
+  </si>
+  <si>
+    <t>Dharampura</t>
+  </si>
+  <si>
+    <t>Tariq Store</t>
+  </si>
+  <si>
+    <t>Express Store</t>
+  </si>
+  <si>
+    <t>Gopal Nager</t>
+  </si>
+  <si>
+    <t>Somroo Sweet</t>
+  </si>
+  <si>
+    <t>haji Chirag</t>
+  </si>
+  <si>
+    <t>Ali subhan GS</t>
+  </si>
+  <si>
+    <t>Agrow Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajwa Mart </t>
+  </si>
+  <si>
+    <t>Kanchi Bazar</t>
+  </si>
+  <si>
+    <t>Defence Store</t>
+  </si>
+  <si>
+    <t>allys Store</t>
+  </si>
+  <si>
+    <t>MS Store</t>
+  </si>
+  <si>
+    <t>usman Store</t>
+  </si>
+  <si>
+    <t>My Choice Store</t>
+  </si>
+  <si>
+    <t>Mahraja Store</t>
+  </si>
+  <si>
+    <t>Adnan ghani Store</t>
+  </si>
+  <si>
+    <t>MHT Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KS Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hafiz Azmat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perdesi Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iqbal Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central Park </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferozpur Road </t>
+  </si>
+  <si>
+    <t>Ismail Nager Lahore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kahna </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muslim Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muslim Town Ayubia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pak Arab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walton Road </t>
+  </si>
+  <si>
+    <t>Youhaba Abad</t>
+  </si>
 </sst>
 </file>
 
@@ -1605,7 +1704,7 @@
     <numFmt numFmtId="166" formatCode="0;[Red]0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1724,6 +1823,14 @@
       <color theme="1" tint="0.34998626667073579"/>
       <name val="Arial Black"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -2211,7 +2318,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2486,22 +2593,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2513,11 +2620,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2536,6 +2643,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2897,44 +3007,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="106" t="s">
+      <c r="A1" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="107" t="s">
+      <c r="C1" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="107" t="s">
+      <c r="D1" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="107" t="s">
+      <c r="E1" s="102" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="107" t="s">
+      <c r="H1" s="102" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="106" t="s">
+      <c r="K1" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="111" t="s">
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
       <c r="S1" s="108" t="s">
         <v>10</v>
       </c>
@@ -2950,61 +3060,61 @@
       <c r="Y1" s="110"/>
       <c r="Z1" s="110"/>
       <c r="AA1" s="110"/>
-      <c r="AB1" s="104" t="s">
+      <c r="AB1" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="104" t="s">
+      <c r="AC1" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="104" t="s">
+      <c r="AD1" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="104" t="s">
+      <c r="AE1" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="104" t="s">
+      <c r="AF1" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="104" t="s">
+      <c r="AG1" s="106" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="104" t="s">
+      <c r="AI1" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="104" t="s">
+      <c r="AJ1" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="104" t="s">
+      <c r="AK1" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="104" t="s">
+      <c r="AL1" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="104" t="s">
+      <c r="AM1" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="102" t="s">
+      <c r="AN1" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="102" t="s">
+      <c r="AO1" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="104" t="s">
+      <c r="AP1" s="106" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="107"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="102"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3060,23 +3170,23 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="105"/>
-      <c r="AC2" s="105"/>
-      <c r="AD2" s="105"/>
-      <c r="AE2" s="105"/>
-      <c r="AF2" s="105"/>
-      <c r="AG2" s="105"/>
+      <c r="AB2" s="107"/>
+      <c r="AC2" s="107"/>
+      <c r="AD2" s="107"/>
+      <c r="AE2" s="107"/>
+      <c r="AF2" s="107"/>
+      <c r="AG2" s="107"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="105"/>
-      <c r="AJ2" s="105"/>
-      <c r="AK2" s="105"/>
-      <c r="AL2" s="105"/>
-      <c r="AM2" s="105"/>
-      <c r="AN2" s="103"/>
-      <c r="AO2" s="103"/>
-      <c r="AP2" s="105"/>
+      <c r="AI2" s="107"/>
+      <c r="AJ2" s="107"/>
+      <c r="AK2" s="107"/>
+      <c r="AL2" s="107"/>
+      <c r="AM2" s="107"/>
+      <c r="AN2" s="112"/>
+      <c r="AO2" s="112"/>
+      <c r="AP2" s="107"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="71">
@@ -50617,13 +50727,33 @@
       <c r="AP364" s="12"/>
     </row>
     <row r="365" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A365" s="17"/>
-      <c r="C365" s="18"/>
-      <c r="E365" s="6"/>
-      <c r="F365" s="19"/>
-      <c r="G365" s="19"/>
-      <c r="H365" s="19"/>
-      <c r="I365" s="6"/>
+      <c r="A365" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B365" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C365" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D365" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E365" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F365" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G365" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="H365" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="I365" s="6" t="s">
+        <v>523</v>
+      </c>
       <c r="J365" s="55"/>
       <c r="K365" s="18"/>
       <c r="L365" s="18"/>
@@ -50632,16 +50762,22 @@
         <f t="shared" si="145"/>
         <v>0</v>
       </c>
-      <c r="O365" s="18"/>
-      <c r="P365" s="20"/>
-      <c r="Q365" s="18"/>
+      <c r="O365" s="18">
+        <v>15</v>
+      </c>
+      <c r="P365" s="20">
+        <v>10</v>
+      </c>
+      <c r="Q365" s="18">
+        <v>15</v>
+      </c>
       <c r="R365" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S365" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T365" s="18">
         <f t="shared" si="137"/>
@@ -50661,19 +50797,19 @@
       </c>
       <c r="X365" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y365" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z365" s="18">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA365" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB365" s="8">
         <v>39.270000000000003</v>
@@ -50686,14 +50822,14 @@
       </c>
       <c r="AE365" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF365" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG365" s="10">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH365" s="64">
         <f t="shared" si="149"/>
@@ -50701,29 +50837,49 @@
       </c>
       <c r="AI365" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ365" s="5">
         <v>0.18</v>
       </c>
       <c r="AK365" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL365" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP365" s="12"/>
     </row>
     <row r="366" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A366" s="17"/>
-      <c r="C366" s="18"/>
-      <c r="E366" s="6"/>
-      <c r="F366" s="19"/>
-      <c r="G366" s="19"/>
-      <c r="H366" s="19"/>
-      <c r="I366" s="6"/>
+      <c r="A366" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B366" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C366" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D366" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E366" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F366" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G366" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="H366" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="I366" s="6" t="s">
+        <v>523</v>
+      </c>
       <c r="J366" s="55"/>
       <c r="K366" s="18"/>
       <c r="L366" s="18"/>
@@ -50732,16 +50888,18 @@
         <f t="shared" si="145"/>
         <v>0</v>
       </c>
-      <c r="O366" s="20"/>
+      <c r="O366" s="20">
+        <v>40</v>
+      </c>
       <c r="P366" s="20"/>
       <c r="Q366" s="20"/>
       <c r="R366" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S366" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T366" s="18">
         <f t="shared" si="137"/>
@@ -50761,7 +50919,7 @@
       </c>
       <c r="X366" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y366" s="18">
         <f t="shared" si="141"/>
@@ -50773,7 +50931,7 @@
       </c>
       <c r="AA366" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB366" s="8">
         <v>39.270000000000003</v>
@@ -50786,14 +50944,14 @@
       </c>
       <c r="AE366" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF366" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG366" s="10">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH366" s="64">
         <f t="shared" si="149"/>
@@ -50801,55 +50959,83 @@
       </c>
       <c r="AI366" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ366" s="5">
         <v>0.18</v>
       </c>
       <c r="AK366" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL366" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP366" s="12"/>
     </row>
     <row r="367" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A367" s="17"/>
-      <c r="C367" s="18"/>
-      <c r="E367" s="6"/>
-      <c r="F367" s="19"/>
-      <c r="G367" s="19"/>
-      <c r="H367" s="19"/>
-      <c r="I367" s="6"/>
+      <c r="A367" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B367" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C367" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D367" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E367" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F367" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="G367" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="H367" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="I367" s="6" t="s">
+        <v>523</v>
+      </c>
       <c r="J367" s="55"/>
-      <c r="K367" s="18"/>
-      <c r="L367" s="20"/>
+      <c r="K367" s="18">
+        <v>20</v>
+      </c>
+      <c r="L367" s="20">
+        <v>20</v>
+      </c>
       <c r="M367" s="20"/>
       <c r="N367" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
-      </c>
-      <c r="O367" s="18"/>
+        <v>40</v>
+      </c>
+      <c r="O367" s="18">
+        <v>20</v>
+      </c>
       <c r="P367" s="20"/>
-      <c r="Q367" s="20"/>
+      <c r="Q367" s="20">
+        <v>20</v>
+      </c>
       <c r="R367" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S367" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T367" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U367" s="18">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V367" s="18">
         <f t="shared" si="139"/>
@@ -50857,11 +51043,11 @@
       </c>
       <c r="W367" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X367" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y367" s="18">
         <f t="shared" si="141"/>
@@ -50869,11 +51055,11 @@
       </c>
       <c r="Z367" s="18">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA367" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB367" s="8">
         <v>39.270000000000003</v>
@@ -50886,14 +51072,14 @@
       </c>
       <c r="AE367" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>7909.7</v>
       </c>
       <c r="AF367" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG367" s="10">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>514.13049999999998</v>
       </c>
       <c r="AH367" s="64">
         <f t="shared" si="149"/>
@@ -50901,29 +51087,49 @@
       </c>
       <c r="AI367" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>7395.5694999999996</v>
       </c>
       <c r="AJ367" s="5">
         <v>0.18</v>
       </c>
       <c r="AK367" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>1331.2025099999998</v>
       </c>
       <c r="AL367" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>8726.7720099999988</v>
       </c>
       <c r="AP367" s="12"/>
     </row>
     <row r="368" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A368" s="17"/>
-      <c r="C368" s="18"/>
-      <c r="E368" s="6"/>
-      <c r="F368" s="19"/>
-      <c r="G368" s="19"/>
-      <c r="H368" s="19"/>
-      <c r="I368" s="6"/>
+      <c r="A368" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B368" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C368" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D368" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E368" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F368" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G368" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="H368" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="I368" s="6" t="s">
+        <v>523</v>
+      </c>
       <c r="J368" s="55"/>
       <c r="K368" s="18"/>
       <c r="L368" s="18"/>
@@ -50932,16 +51138,22 @@
         <f t="shared" si="145"/>
         <v>0</v>
       </c>
-      <c r="O368" s="20"/>
-      <c r="P368" s="20"/>
-      <c r="Q368" s="20"/>
+      <c r="O368" s="20">
+        <v>80</v>
+      </c>
+      <c r="P368" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q368" s="20">
+        <v>80</v>
+      </c>
       <c r="R368" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S368" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T368" s="18">
         <f t="shared" si="137"/>
@@ -50961,19 +51173,19 @@
       </c>
       <c r="X368" s="18">
         <f t="shared" si="140"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y368" s="18">
         <f t="shared" si="141"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z368" s="18">
         <f t="shared" si="142"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA368" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB368" s="8">
         <v>39.270000000000003</v>
@@ -50986,14 +51198,14 @@
       </c>
       <c r="AE368" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>14528</v>
       </c>
       <c r="AF368" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG368" s="10">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>944.32</v>
       </c>
       <c r="AH368" s="64">
         <f t="shared" si="149"/>
@@ -51001,36 +51213,60 @@
       </c>
       <c r="AI368" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>13583.68</v>
       </c>
       <c r="AJ368" s="5">
         <v>0.18</v>
       </c>
       <c r="AK368" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>2445.0623999999998</v>
       </c>
       <c r="AL368" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>16028.742399999999</v>
       </c>
       <c r="AP368" s="12"/>
     </row>
     <row r="369" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A369" s="17"/>
-      <c r="C369" s="18"/>
-      <c r="E369" s="6"/>
-      <c r="F369" s="19"/>
-      <c r="G369" s="19"/>
-      <c r="H369" s="19"/>
-      <c r="I369" s="6"/>
+      <c r="A369" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B369" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C369" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D369" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E369" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F369" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G369" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="H369" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="I369" s="6" t="s">
+        <v>526</v>
+      </c>
       <c r="J369" s="55"/>
-      <c r="K369" s="20"/>
-      <c r="L369" s="20"/>
+      <c r="K369" s="20">
+        <v>20</v>
+      </c>
+      <c r="L369" s="20">
+        <v>20</v>
+      </c>
       <c r="M369" s="20"/>
       <c r="N369" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O369" s="20"/>
       <c r="P369" s="20"/>
@@ -51041,15 +51277,15 @@
       </c>
       <c r="S369" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T369" s="18">
         <f t="shared" si="137"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U369" s="18">
         <f t="shared" si="138"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V369" s="18">
         <f t="shared" si="139"/>
@@ -51057,7 +51293,7 @@
       </c>
       <c r="W369" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X369" s="18">
         <f t="shared" si="140"/>
@@ -51086,14 +51322,14 @@
       </c>
       <c r="AE369" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>5004.1000000000004</v>
       </c>
       <c r="AF369" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG369" s="10">
         <f t="shared" si="143"/>
-        <v>0</v>
+        <v>325.26650000000001</v>
       </c>
       <c r="AH369" s="64">
         <f t="shared" si="149"/>
@@ -51101,29 +51337,49 @@
       </c>
       <c r="AI369" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>4678.8335000000006</v>
       </c>
       <c r="AJ369" s="5">
         <v>0.18</v>
       </c>
       <c r="AK369" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>842.19003000000009</v>
       </c>
       <c r="AL369" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>5521.0235300000004</v>
       </c>
       <c r="AP369" s="12"/>
     </row>
     <row r="370" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A370" s="17"/>
-      <c r="C370" s="18"/>
-      <c r="E370" s="6"/>
-      <c r="F370" s="19"/>
-      <c r="G370" s="19"/>
-      <c r="H370" s="19"/>
-      <c r="I370" s="6"/>
+      <c r="A370" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B370" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C370" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D370" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E370" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F370" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G370" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="H370" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="I370" s="6" t="s">
+        <v>526</v>
+      </c>
       <c r="J370" s="55"/>
       <c r="K370" s="18"/>
       <c r="L370" s="18"/>
@@ -51134,14 +51390,16 @@
       </c>
       <c r="O370" s="18"/>
       <c r="P370" s="18"/>
-      <c r="Q370" s="18"/>
+      <c r="Q370" s="18">
+        <v>20</v>
+      </c>
       <c r="R370" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S370" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T370" s="18">
         <f t="shared" ref="T370:T420" si="154">K370/10</f>
@@ -51169,11 +51427,11 @@
       </c>
       <c r="Z370" s="18">
         <f t="shared" ref="Z370:Z420" si="159">Q370/10</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA370" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB370" s="8">
         <v>39.270000000000003</v>
@@ -51186,14 +51444,14 @@
       </c>
       <c r="AE370" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="AF370" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG370" s="10">
         <f t="shared" ref="AG370:AG420" si="160">AE370*AF370</f>
-        <v>0</v>
+        <v>203.39200000000002</v>
       </c>
       <c r="AH370" s="64">
         <f t="shared" si="149"/>
@@ -51201,55 +51459,85 @@
       </c>
       <c r="AI370" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1249.4079999999999</v>
       </c>
       <c r="AJ370" s="5">
         <v>0.18</v>
       </c>
       <c r="AK370" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>224.89343999999997</v>
       </c>
       <c r="AL370" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1474.30144</v>
       </c>
       <c r="AP370" s="12"/>
     </row>
     <row r="371" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A371" s="17"/>
-      <c r="C371" s="18"/>
-      <c r="E371" s="6"/>
-      <c r="F371" s="19"/>
-      <c r="G371" s="19"/>
-      <c r="H371" s="19"/>
-      <c r="I371" s="6"/>
+      <c r="A371" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B371" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C371" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D371" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E371" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F371" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G371" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="H371" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="I371" s="6" t="s">
+        <v>526</v>
+      </c>
       <c r="J371" s="55"/>
-      <c r="K371" s="18"/>
-      <c r="L371" s="18"/>
+      <c r="K371" s="18">
+        <v>10</v>
+      </c>
+      <c r="L371" s="18">
+        <v>10</v>
+      </c>
       <c r="M371" s="18"/>
       <c r="N371" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
-      </c>
-      <c r="O371" s="18"/>
-      <c r="P371" s="18"/>
-      <c r="Q371" s="18"/>
+        <v>20</v>
+      </c>
+      <c r="O371" s="18">
+        <v>10</v>
+      </c>
+      <c r="P371" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q371" s="18">
+        <v>10</v>
+      </c>
       <c r="R371" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S371" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T371" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U371" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V371" s="18">
         <f t="shared" si="156"/>
@@ -51257,23 +51545,23 @@
       </c>
       <c r="W371" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X371" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y371" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z371" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA371" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB371" s="8">
         <v>39.270000000000003</v>
@@ -51286,14 +51574,14 @@
       </c>
       <c r="AE371" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>4681.25</v>
       </c>
       <c r="AF371" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG371" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>655.37500000000011</v>
       </c>
       <c r="AH371" s="64">
         <f t="shared" si="149"/>
@@ -51301,30 +51589,52 @@
       </c>
       <c r="AI371" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>4025.875</v>
       </c>
       <c r="AJ371" s="5">
         <v>0.18</v>
       </c>
       <c r="AK371" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>724.65750000000003</v>
       </c>
       <c r="AL371" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>4750.5325000000003</v>
       </c>
       <c r="AP371" s="12"/>
     </row>
     <row r="372" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A372" s="17"/>
-      <c r="C372" s="18"/>
-      <c r="E372" s="6"/>
-      <c r="F372" s="19"/>
-      <c r="G372" s="19"/>
-      <c r="H372" s="19"/>
-      <c r="I372" s="6"/>
-      <c r="J372" s="55"/>
+      <c r="A372" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B372" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C372" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D372" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E372" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F372" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G372" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="H372" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I372" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="J372" s="55">
+        <v>12</v>
+      </c>
       <c r="K372" s="18"/>
       <c r="L372" s="18"/>
       <c r="M372" s="18"/>
@@ -51341,7 +51651,7 @@
       </c>
       <c r="S372" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T372" s="18">
         <f t="shared" si="154"/>
@@ -51386,45 +51696,67 @@
       </c>
       <c r="AE372" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1342.92</v>
       </c>
       <c r="AF372" s="21">
         <v>0.15</v>
       </c>
       <c r="AG372" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>201.43800000000002</v>
       </c>
       <c r="AH372" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI372" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1141.482</v>
       </c>
       <c r="AJ372" s="5">
         <v>0.18</v>
       </c>
       <c r="AK372" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>205.46675999999999</v>
       </c>
       <c r="AL372" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1346.94876</v>
       </c>
       <c r="AP372" s="12"/>
     </row>
     <row r="373" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A373" s="17"/>
-      <c r="C373" s="18"/>
-      <c r="E373" s="6"/>
-      <c r="F373" s="19"/>
-      <c r="G373" s="19"/>
-      <c r="H373" s="19"/>
-      <c r="I373" s="6"/>
-      <c r="J373" s="55"/>
+      <c r="A373" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B373" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C373" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D373" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E373" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F373" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G373" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="H373" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I373" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="J373" s="55">
+        <v>40</v>
+      </c>
       <c r="K373" s="20"/>
       <c r="L373" s="20"/>
       <c r="M373" s="18"/>
@@ -51441,7 +51773,7 @@
       </c>
       <c r="S373" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T373" s="18">
         <f t="shared" si="154"/>
@@ -51486,51 +51818,77 @@
       </c>
       <c r="AE373" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF373" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG373" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH373" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI373" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ373" s="5">
         <v>0.18</v>
       </c>
       <c r="AK373" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL373" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP373" s="12"/>
     </row>
     <row r="374" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A374" s="17"/>
-      <c r="C374" s="18"/>
-      <c r="E374" s="6"/>
-      <c r="F374" s="19"/>
-      <c r="G374" s="19"/>
-      <c r="H374" s="19"/>
-      <c r="I374" s="6"/>
-      <c r="J374" s="55"/>
-      <c r="K374" s="18"/>
-      <c r="L374" s="18"/>
+      <c r="A374" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B374" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C374" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D374" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E374" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F374" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G374" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="H374" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I374" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="J374" s="55">
+        <v>10</v>
+      </c>
+      <c r="K374" s="18">
+        <v>15</v>
+      </c>
+      <c r="L374" s="18">
+        <v>15</v>
+      </c>
       <c r="M374" s="18"/>
       <c r="N374" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O374" s="18"/>
       <c r="P374" s="18"/>
@@ -51541,15 +51899,15 @@
       </c>
       <c r="S374" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T374" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U374" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V374" s="18">
         <f t="shared" si="156"/>
@@ -51557,7 +51915,7 @@
       </c>
       <c r="W374" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X374" s="18">
         <f t="shared" si="157"/>
@@ -51586,45 +51944,67 @@
       </c>
       <c r="AE374" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>4872.1750000000002</v>
       </c>
       <c r="AF374" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG374" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>316.69137500000005</v>
       </c>
       <c r="AH374" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI374" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>4555.4836249999998</v>
       </c>
       <c r="AJ374" s="5">
         <v>0.18</v>
       </c>
       <c r="AK374" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>819.98705249999989</v>
       </c>
       <c r="AL374" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>5375.4706774999995</v>
       </c>
       <c r="AP374" s="12"/>
     </row>
     <row r="375" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A375" s="17"/>
-      <c r="C375" s="18"/>
-      <c r="E375" s="6"/>
-      <c r="F375" s="19"/>
-      <c r="G375" s="19"/>
-      <c r="H375" s="19"/>
-      <c r="I375" s="6"/>
-      <c r="J375" s="55"/>
+      <c r="A375" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B375" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C375" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D375" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E375" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F375" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G375" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="H375" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I375" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="J375" s="55">
+        <v>10</v>
+      </c>
       <c r="K375" s="20"/>
       <c r="L375" s="20"/>
       <c r="M375" s="20"/>
@@ -51641,7 +52021,7 @@
       </c>
       <c r="S375" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T375" s="18">
         <f t="shared" si="154"/>
@@ -51686,45 +52066,67 @@
       </c>
       <c r="AE375" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF375" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG375" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH375" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI375" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ375" s="5">
         <v>0.18</v>
       </c>
       <c r="AK375" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL375" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP375" s="12"/>
     </row>
     <row r="376" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A376" s="17"/>
-      <c r="C376" s="18"/>
-      <c r="E376" s="6"/>
-      <c r="F376" s="19"/>
-      <c r="G376" s="19"/>
-      <c r="H376" s="19"/>
-      <c r="I376" s="6"/>
-      <c r="J376" s="55"/>
+      <c r="A376" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B376" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C376" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D376" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E376" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F376" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G376" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="H376" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I376" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="J376" s="55">
+        <v>40</v>
+      </c>
       <c r="K376" s="20"/>
       <c r="L376" s="20"/>
       <c r="M376" s="20"/>
@@ -51741,7 +52143,7 @@
       </c>
       <c r="S376" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T376" s="18">
         <f t="shared" si="154"/>
@@ -51786,45 +52188,67 @@
       </c>
       <c r="AE376" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF376" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG376" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH376" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI376" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ376" s="5">
         <v>0.18</v>
       </c>
       <c r="AK376" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL376" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP376" s="12"/>
     </row>
     <row r="377" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A377" s="17"/>
-      <c r="C377" s="18"/>
-      <c r="E377" s="6"/>
-      <c r="F377" s="19"/>
-      <c r="G377" s="19"/>
-      <c r="H377" s="19"/>
-      <c r="I377" s="6"/>
-      <c r="J377" s="55"/>
+      <c r="A377" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B377" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C377" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D377" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E377" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F377" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="G377" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="H377" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="I377" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="J377" s="55">
+        <v>40</v>
+      </c>
       <c r="K377" s="20"/>
       <c r="L377" s="20"/>
       <c r="M377" s="20"/>
@@ -51841,7 +52265,7 @@
       </c>
       <c r="S377" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T377" s="18">
         <f t="shared" si="154"/>
@@ -51886,70 +52310,100 @@
       </c>
       <c r="AE377" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF377" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG377" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH377" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI377" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ377" s="5">
         <v>0.18</v>
       </c>
       <c r="AK377" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL377" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP377" s="12"/>
     </row>
     <row r="378" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A378" s="17"/>
-      <c r="C378" s="18"/>
-      <c r="E378" s="6"/>
-      <c r="F378" s="19"/>
-      <c r="G378" s="19"/>
-      <c r="H378" s="19"/>
-      <c r="I378" s="6"/>
-      <c r="J378" s="55"/>
-      <c r="K378" s="20"/>
-      <c r="L378" s="20"/>
+      <c r="A378" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B378" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C378" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D378" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E378" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F378" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G378" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="H378" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I378" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J378" s="55">
+        <v>20</v>
+      </c>
+      <c r="K378" s="20">
+        <v>20</v>
+      </c>
+      <c r="L378" s="20">
+        <v>20</v>
+      </c>
       <c r="M378" s="18"/>
       <c r="N378" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O378" s="18"/>
-      <c r="P378" s="18"/>
-      <c r="Q378" s="18"/>
+      <c r="P378" s="18">
+        <v>20</v>
+      </c>
+      <c r="Q378" s="18">
+        <v>20</v>
+      </c>
       <c r="R378" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S378" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T378" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U378" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V378" s="18">
         <f t="shared" si="156"/>
@@ -51957,7 +52411,7 @@
       </c>
       <c r="W378" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X378" s="18">
         <f t="shared" si="157"/>
@@ -51965,15 +52419,15 @@
       </c>
       <c r="Y378" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z378" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA378" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB378" s="8">
         <v>39.270000000000003</v>
@@ -51986,70 +52440,100 @@
       </c>
       <c r="AE378" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>10147.9</v>
       </c>
       <c r="AF378" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG378" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>659.61350000000004</v>
       </c>
       <c r="AH378" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI378" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>9488.2865000000002</v>
       </c>
       <c r="AJ378" s="5">
         <v>0.18</v>
       </c>
       <c r="AK378" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>1707.89157</v>
       </c>
       <c r="AL378" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>11196.17807</v>
       </c>
       <c r="AP378" s="12"/>
     </row>
     <row r="379" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A379" s="17"/>
-      <c r="C379" s="18"/>
-      <c r="E379" s="6"/>
-      <c r="F379" s="19"/>
-      <c r="G379" s="19"/>
-      <c r="H379" s="19"/>
-      <c r="I379" s="6"/>
+      <c r="A379" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B379" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C379" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D379" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E379" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F379" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G379" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="H379" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I379" s="6" t="s">
+        <v>310</v>
+      </c>
       <c r="J379" s="55"/>
-      <c r="K379" s="20"/>
-      <c r="L379" s="20"/>
+      <c r="K379" s="20">
+        <v>10</v>
+      </c>
+      <c r="L379" s="20">
+        <v>10</v>
+      </c>
       <c r="M379" s="20"/>
       <c r="N379" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
-      </c>
-      <c r="O379" s="18"/>
-      <c r="P379" s="20"/>
-      <c r="Q379" s="18"/>
+        <v>20</v>
+      </c>
+      <c r="O379" s="18">
+        <v>6</v>
+      </c>
+      <c r="P379" s="20">
+        <v>6</v>
+      </c>
+      <c r="Q379" s="18">
+        <v>8</v>
+      </c>
       <c r="R379" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S379" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T379" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U379" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V379" s="18">
         <f t="shared" si="156"/>
@@ -52057,23 +52541,23 @@
       </c>
       <c r="W379" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X379" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Y379" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Z379" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AA379" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB379" s="8">
         <v>39.270000000000003</v>
@@ -52086,14 +52570,14 @@
       </c>
       <c r="AE379" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>3954.85</v>
       </c>
       <c r="AF379" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG379" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>257.06524999999999</v>
       </c>
       <c r="AH379" s="64">
         <f t="shared" si="149"/>
@@ -52101,29 +52585,49 @@
       </c>
       <c r="AI379" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>3697.7847499999998</v>
       </c>
       <c r="AJ379" s="5">
         <v>0.18</v>
       </c>
       <c r="AK379" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>665.60125499999992</v>
       </c>
       <c r="AL379" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>4363.3860049999994</v>
       </c>
       <c r="AP379" s="12"/>
     </row>
     <row r="380" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A380" s="17"/>
-      <c r="C380" s="18"/>
-      <c r="E380" s="6"/>
-      <c r="F380" s="19"/>
-      <c r="G380" s="19"/>
-      <c r="H380" s="19"/>
-      <c r="I380" s="6"/>
+      <c r="A380" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B380" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C380" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D380" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E380" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F380" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G380" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="H380" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I380" s="6" t="s">
+        <v>310</v>
+      </c>
       <c r="J380" s="55"/>
       <c r="K380" s="20"/>
       <c r="L380" s="18"/>
@@ -52132,16 +52636,22 @@
         <f t="shared" si="145"/>
         <v>0</v>
       </c>
-      <c r="O380" s="18"/>
-      <c r="P380" s="18"/>
-      <c r="Q380" s="18"/>
+      <c r="O380" s="18">
+        <v>15</v>
+      </c>
+      <c r="P380" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q380" s="18">
+        <v>15</v>
+      </c>
       <c r="R380" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S380" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T380" s="18">
         <f t="shared" si="154"/>
@@ -52161,19 +52671,19 @@
       </c>
       <c r="X380" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y380" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z380" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA380" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB380" s="8">
         <v>39.270000000000003</v>
@@ -52186,14 +52696,14 @@
       </c>
       <c r="AE380" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF380" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG380" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH380" s="64">
         <f t="shared" si="149"/>
@@ -52201,36 +52711,60 @@
       </c>
       <c r="AI380" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ380" s="5">
         <v>0.18</v>
       </c>
       <c r="AK380" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL380" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP380" s="12"/>
     </row>
     <row r="381" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A381" s="17"/>
-      <c r="C381" s="18"/>
-      <c r="E381" s="6"/>
-      <c r="F381" s="19"/>
-      <c r="G381" s="19"/>
-      <c r="H381" s="19"/>
-      <c r="I381" s="6"/>
+      <c r="A381" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B381" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C381" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D381" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E381" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F381" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G381" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="H381" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I381" s="6" t="s">
+        <v>310</v>
+      </c>
       <c r="J381" s="55"/>
-      <c r="K381" s="20"/>
-      <c r="L381" s="20"/>
+      <c r="K381" s="20">
+        <v>20</v>
+      </c>
+      <c r="L381" s="20">
+        <v>20</v>
+      </c>
       <c r="M381" s="20"/>
       <c r="N381" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O381" s="18"/>
       <c r="P381" s="18"/>
@@ -52241,15 +52775,15 @@
       </c>
       <c r="S381" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T381" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U381" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V381" s="18">
         <f t="shared" si="156"/>
@@ -52257,7 +52791,7 @@
       </c>
       <c r="W381" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X381" s="18">
         <f t="shared" si="157"/>
@@ -52286,14 +52820,14 @@
       </c>
       <c r="AE381" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>5004.1000000000004</v>
       </c>
       <c r="AF381" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG381" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>325.26650000000001</v>
       </c>
       <c r="AH381" s="64">
         <f t="shared" si="149"/>
@@ -52301,29 +52835,49 @@
       </c>
       <c r="AI381" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>4678.8335000000006</v>
       </c>
       <c r="AJ381" s="5">
         <v>0.18</v>
       </c>
       <c r="AK381" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>842.19003000000009</v>
       </c>
       <c r="AL381" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>5521.0235300000004</v>
       </c>
       <c r="AP381" s="12"/>
     </row>
     <row r="382" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A382" s="17"/>
-      <c r="C382" s="18"/>
-      <c r="E382" s="6"/>
-      <c r="F382" s="19"/>
-      <c r="G382" s="19"/>
-      <c r="H382" s="19"/>
-      <c r="I382" s="6"/>
+      <c r="A382" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B382" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C382" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D382" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E382" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F382" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G382" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="H382" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I382" s="6" t="s">
+        <v>310</v>
+      </c>
       <c r="J382" s="55"/>
       <c r="K382" s="20"/>
       <c r="L382" s="20"/>
@@ -52332,16 +52886,22 @@
         <f t="shared" si="145"/>
         <v>0</v>
       </c>
-      <c r="O382" s="18"/>
-      <c r="P382" s="18"/>
-      <c r="Q382" s="20"/>
+      <c r="O382" s="18">
+        <v>15</v>
+      </c>
+      <c r="P382" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q382" s="20">
+        <v>15</v>
+      </c>
       <c r="R382" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S382" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T382" s="18">
         <f t="shared" si="154"/>
@@ -52361,19 +52921,19 @@
       </c>
       <c r="X382" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y382" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z382" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA382" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB382" s="8">
         <v>39.270000000000003</v>
@@ -52386,14 +52946,14 @@
       </c>
       <c r="AE382" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF382" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG382" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH382" s="64">
         <f t="shared" si="149"/>
@@ -52401,55 +52961,87 @@
       </c>
       <c r="AI382" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ382" s="5">
         <v>0.18</v>
       </c>
       <c r="AK382" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL382" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP382" s="12"/>
     </row>
     <row r="383" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A383" s="17"/>
-      <c r="C383" s="18"/>
-      <c r="E383" s="6"/>
-      <c r="F383" s="19"/>
-      <c r="G383" s="19"/>
-      <c r="H383" s="19"/>
-      <c r="I383" s="6"/>
-      <c r="J383" s="55"/>
-      <c r="K383" s="18"/>
-      <c r="L383" s="18"/>
+      <c r="A383" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B383" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C383" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D383" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E383" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F383" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G383" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="H383" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I383" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J383" s="55">
+        <v>40</v>
+      </c>
+      <c r="K383" s="18">
+        <v>20</v>
+      </c>
+      <c r="L383" s="18">
+        <v>20</v>
+      </c>
       <c r="M383" s="18"/>
       <c r="N383" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
-      </c>
-      <c r="O383" s="18"/>
-      <c r="P383" s="18"/>
-      <c r="Q383" s="18"/>
+        <v>40</v>
+      </c>
+      <c r="O383" s="18">
+        <v>15</v>
+      </c>
+      <c r="P383" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q383" s="18">
+        <v>15</v>
+      </c>
       <c r="R383" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S383" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="T383" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U383" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V383" s="18">
         <f t="shared" si="156"/>
@@ -52457,23 +53049,23 @@
       </c>
       <c r="W383" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X383" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y383" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z383" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA383" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB383" s="8">
         <v>39.270000000000003</v>
@@ -52486,70 +53078,102 @@
       </c>
       <c r="AE383" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>12386.099999999999</v>
       </c>
       <c r="AF383" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG383" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>805.09649999999988</v>
       </c>
       <c r="AH383" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI383" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>11581.003499999999</v>
       </c>
       <c r="AJ383" s="5">
         <v>0.18</v>
       </c>
       <c r="AK383" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>2084.5806299999999</v>
       </c>
       <c r="AL383" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>13665.584129999999</v>
       </c>
       <c r="AP383" s="12"/>
     </row>
     <row r="384" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A384" s="17"/>
-      <c r="C384" s="18"/>
-      <c r="E384" s="6"/>
-      <c r="F384" s="19"/>
-      <c r="G384" s="19"/>
-      <c r="H384" s="19"/>
-      <c r="I384" s="6"/>
-      <c r="J384" s="55"/>
-      <c r="K384" s="20"/>
-      <c r="L384" s="20"/>
+      <c r="A384" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B384" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C384" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D384" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E384" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F384" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G384" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="H384" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I384" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J384" s="55">
+        <v>40</v>
+      </c>
+      <c r="K384" s="20">
+        <v>20</v>
+      </c>
+      <c r="L384" s="20">
+        <v>20</v>
+      </c>
       <c r="M384" s="20"/>
       <c r="N384" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
-      </c>
-      <c r="O384" s="18"/>
-      <c r="P384" s="18"/>
-      <c r="Q384" s="20"/>
+        <v>40</v>
+      </c>
+      <c r="O384" s="18">
+        <v>15</v>
+      </c>
+      <c r="P384" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q384" s="20">
+        <v>15</v>
+      </c>
       <c r="R384" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S384" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="T384" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U384" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V384" s="18">
         <f t="shared" si="156"/>
@@ -52557,23 +53181,23 @@
       </c>
       <c r="W384" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X384" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y384" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z384" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA384" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB384" s="8">
         <v>39.270000000000003</v>
@@ -52586,45 +53210,67 @@
       </c>
       <c r="AE384" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>12386.099999999999</v>
       </c>
       <c r="AF384" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG384" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>805.09649999999988</v>
       </c>
       <c r="AH384" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI384" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>11581.003499999999</v>
       </c>
       <c r="AJ384" s="5">
         <v>0.18</v>
       </c>
       <c r="AK384" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>2084.5806299999999</v>
       </c>
       <c r="AL384" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>13665.584129999999</v>
       </c>
       <c r="AP384" s="12"/>
     </row>
     <row r="385" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A385" s="17"/>
-      <c r="C385" s="18"/>
-      <c r="E385" s="6"/>
-      <c r="F385" s="19"/>
-      <c r="G385" s="19"/>
-      <c r="H385" s="19"/>
-      <c r="I385" s="6"/>
-      <c r="J385" s="6"/>
+      <c r="A385" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B385" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C385" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D385" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E385" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F385" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G385" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="H385" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I385" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J385" s="6">
+        <v>40</v>
+      </c>
       <c r="K385" s="20"/>
       <c r="L385" s="20"/>
       <c r="M385" s="20"/>
@@ -52632,16 +53278,22 @@
         <f t="shared" si="145"/>
         <v>0</v>
       </c>
-      <c r="O385" s="18"/>
-      <c r="P385" s="18"/>
-      <c r="Q385" s="20"/>
+      <c r="O385" s="18">
+        <v>15</v>
+      </c>
+      <c r="P385" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q385" s="20">
+        <v>15</v>
+      </c>
       <c r="R385" s="8">
         <f t="shared" si="144"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S385" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T385" s="18">
         <f t="shared" si="154"/>
@@ -52661,19 +53313,19 @@
       </c>
       <c r="X385" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y385" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z385" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA385" s="8">
         <f t="shared" si="147"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB385" s="8">
         <v>39.270000000000003</v>
@@ -52686,45 +53338,67 @@
       </c>
       <c r="AE385" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>7382</v>
       </c>
       <c r="AF385" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG385" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>479.83000000000004</v>
       </c>
       <c r="AH385" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI385" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>6902.17</v>
       </c>
       <c r="AJ385" s="5">
         <v>0.18</v>
       </c>
       <c r="AK385" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>1242.3905999999999</v>
       </c>
       <c r="AL385" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>8144.5605999999998</v>
       </c>
       <c r="AP385" s="12"/>
     </row>
     <row r="386" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A386" s="17"/>
-      <c r="C386" s="18"/>
-      <c r="E386" s="6"/>
-      <c r="F386" s="19"/>
-      <c r="G386" s="19"/>
-      <c r="H386" s="19"/>
-      <c r="I386" s="6"/>
-      <c r="J386" s="6"/>
+      <c r="A386" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B386" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C386" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D386" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E386" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F386" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G386" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="H386" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I386" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J386" s="6">
+        <v>10</v>
+      </c>
       <c r="K386" s="20"/>
       <c r="L386" s="20"/>
       <c r="M386" s="20"/>
@@ -52741,7 +53415,7 @@
       </c>
       <c r="S386" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T386" s="18">
         <f t="shared" si="154"/>
@@ -52786,51 +53460,77 @@
       </c>
       <c r="AE386" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF386" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG386" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH386" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI386" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ386" s="5">
         <v>0.18</v>
       </c>
       <c r="AK386" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL386" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP386" s="12"/>
     </row>
     <row r="387" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A387" s="17"/>
-      <c r="C387" s="18"/>
-      <c r="E387" s="6"/>
-      <c r="F387" s="19"/>
-      <c r="G387" s="19"/>
-      <c r="H387" s="19"/>
-      <c r="I387" s="6"/>
-      <c r="J387" s="6"/>
-      <c r="K387" s="20"/>
-      <c r="L387" s="20"/>
+      <c r="A387" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B387" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C387" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D387" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E387" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F387" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G387" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="H387" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I387" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J387" s="6">
+        <v>10</v>
+      </c>
+      <c r="K387" s="20">
+        <v>6</v>
+      </c>
+      <c r="L387" s="20">
+        <v>6</v>
+      </c>
       <c r="M387" s="20"/>
       <c r="N387" s="8">
         <f t="shared" si="145"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O387" s="20"/>
       <c r="P387" s="18"/>
@@ -52841,15 +53541,15 @@
       </c>
       <c r="S387" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T387" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="U387" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V387" s="18">
         <f t="shared" si="156"/>
@@ -52857,7 +53557,7 @@
       </c>
       <c r="W387" s="8">
         <f t="shared" si="146"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X387" s="18">
         <f t="shared" si="157"/>
@@ -52886,45 +53586,67 @@
       </c>
       <c r="AE387" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>2620.33</v>
       </c>
       <c r="AF387" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG387" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>170.32145</v>
       </c>
       <c r="AH387" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI387" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>2450.00855</v>
       </c>
       <c r="AJ387" s="5">
         <v>0.18</v>
       </c>
       <c r="AK387" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>441.00153899999998</v>
       </c>
       <c r="AL387" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>2891.0100889999999</v>
       </c>
       <c r="AP387" s="12"/>
     </row>
     <row r="388" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A388" s="17"/>
-      <c r="C388" s="18"/>
-      <c r="E388" s="6"/>
-      <c r="F388" s="19"/>
-      <c r="G388" s="19"/>
-      <c r="H388" s="19"/>
-      <c r="I388" s="6"/>
-      <c r="J388" s="6"/>
+      <c r="A388" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B388" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C388" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D388" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E388" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F388" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G388" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="H388" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I388" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J388" s="6">
+        <v>10</v>
+      </c>
       <c r="K388" s="18"/>
       <c r="L388" s="18"/>
       <c r="M388" s="18"/>
@@ -52941,7 +53663,7 @@
       </c>
       <c r="S388" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T388" s="18">
         <f t="shared" si="154"/>
@@ -52986,45 +53708,67 @@
       </c>
       <c r="AE388" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF388" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG388" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH388" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI388" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ388" s="5">
         <v>0.18</v>
       </c>
       <c r="AK388" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL388" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP388" s="12"/>
     </row>
     <row r="389" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A389" s="17"/>
-      <c r="C389" s="18"/>
-      <c r="E389" s="6"/>
-      <c r="F389" s="19"/>
-      <c r="G389" s="19"/>
-      <c r="H389" s="19"/>
-      <c r="I389" s="6"/>
-      <c r="J389" s="6"/>
+      <c r="A389" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B389" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C389" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D389" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E389" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F389" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G389" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="H389" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I389" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J389" s="6">
+        <v>10</v>
+      </c>
       <c r="K389" s="20"/>
       <c r="L389" s="20"/>
       <c r="M389" s="20"/>
@@ -53041,7 +53785,7 @@
       </c>
       <c r="S389" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T389" s="18">
         <f t="shared" si="154"/>
@@ -53086,45 +53830,67 @@
       </c>
       <c r="AE389" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF389" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG389" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH389" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI389" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ389" s="5">
         <v>0.18</v>
       </c>
       <c r="AK389" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL389" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP389" s="12"/>
     </row>
     <row r="390" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A390" s="17"/>
-      <c r="C390" s="18"/>
-      <c r="E390" s="6"/>
-      <c r="F390" s="19"/>
-      <c r="G390" s="19"/>
-      <c r="H390" s="19"/>
-      <c r="I390" s="6"/>
-      <c r="J390" s="6"/>
+      <c r="A390" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B390" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C390" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D390" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E390" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F390" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G390" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="H390" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I390" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J390" s="6">
+        <v>10</v>
+      </c>
       <c r="K390" s="20"/>
       <c r="L390" s="20"/>
       <c r="M390" s="20"/>
@@ -53141,7 +53907,7 @@
       </c>
       <c r="S390" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T390" s="18">
         <f t="shared" si="154"/>
@@ -53186,45 +53952,67 @@
       </c>
       <c r="AE390" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF390" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG390" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH390" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI390" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ390" s="5">
         <v>0.18</v>
       </c>
       <c r="AK390" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL390" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP390" s="12"/>
     </row>
     <row r="391" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A391" s="17"/>
-      <c r="C391" s="18"/>
-      <c r="E391" s="6"/>
-      <c r="F391" s="19"/>
-      <c r="G391" s="19"/>
-      <c r="H391" s="19"/>
-      <c r="I391" s="6"/>
-      <c r="J391" s="6"/>
+      <c r="A391" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B391" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C391" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D391" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E391" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F391" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G391" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="H391" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I391" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J391" s="6">
+        <v>10</v>
+      </c>
       <c r="K391" s="20"/>
       <c r="L391" s="20"/>
       <c r="M391" s="20"/>
@@ -53241,7 +54029,7 @@
       </c>
       <c r="S391" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T391" s="18">
         <f t="shared" si="154"/>
@@ -53286,45 +54074,67 @@
       </c>
       <c r="AE391" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF391" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG391" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH391" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI391" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ391" s="5">
         <v>0.18</v>
       </c>
       <c r="AK391" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL391" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP391" s="12"/>
     </row>
     <row r="392" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A392" s="17"/>
-      <c r="C392" s="18"/>
-      <c r="E392" s="6"/>
-      <c r="F392" s="19"/>
-      <c r="G392" s="19"/>
-      <c r="H392" s="19"/>
-      <c r="I392" s="6"/>
-      <c r="J392" s="6"/>
+      <c r="A392" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B392" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C392" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D392" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E392" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F392" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="G392" s="19" t="s">
+        <v>541</v>
+      </c>
+      <c r="H392" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I392" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J392" s="6">
+        <v>10</v>
+      </c>
       <c r="K392" s="18"/>
       <c r="L392" s="18"/>
       <c r="M392" s="18"/>
@@ -53341,7 +54151,7 @@
       </c>
       <c r="S392" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T392" s="18">
         <f t="shared" si="154"/>
@@ -53386,45 +54196,67 @@
       </c>
       <c r="AE392" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF392" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG392" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>156.67400000000001</v>
       </c>
       <c r="AH392" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI392" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>962.42599999999993</v>
       </c>
       <c r="AJ392" s="5">
         <v>0.18</v>
       </c>
       <c r="AK392" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>173.23667999999998</v>
       </c>
       <c r="AL392" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1135.6626799999999</v>
       </c>
       <c r="AP392" s="12"/>
     </row>
     <row r="393" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A393" s="17"/>
-      <c r="C393" s="18"/>
-      <c r="E393" s="6"/>
-      <c r="F393" s="19"/>
-      <c r="G393" s="19"/>
-      <c r="H393" s="19"/>
-      <c r="I393" s="6"/>
-      <c r="J393" s="6"/>
+      <c r="A393" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B393" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C393" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D393" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E393" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F393" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="G393" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="H393" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I393" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J393" s="6">
+        <v>10</v>
+      </c>
       <c r="K393" s="18"/>
       <c r="L393" s="18"/>
       <c r="M393" s="18"/>
@@ -53441,7 +54273,7 @@
       </c>
       <c r="S393" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T393" s="18">
         <f t="shared" si="154"/>
@@ -53486,45 +54318,67 @@
       </c>
       <c r="AE393" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF393" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG393" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>156.67400000000001</v>
       </c>
       <c r="AH393" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI393" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>962.42599999999993</v>
       </c>
       <c r="AJ393" s="5">
         <v>0.18</v>
       </c>
       <c r="AK393" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>173.23667999999998</v>
       </c>
       <c r="AL393" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>1135.6626799999999</v>
       </c>
       <c r="AP393" s="12"/>
     </row>
     <row r="394" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A394" s="17"/>
-      <c r="C394" s="18"/>
-      <c r="E394" s="6"/>
-      <c r="F394" s="19"/>
-      <c r="G394" s="19"/>
-      <c r="H394" s="19"/>
-      <c r="I394" s="6"/>
-      <c r="J394" s="6"/>
+      <c r="A394" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B394" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C394" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D394" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E394" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F394" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="G394" s="19" t="s">
+        <v>543</v>
+      </c>
+      <c r="H394" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I394" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J394" s="6">
+        <v>40</v>
+      </c>
       <c r="K394" s="20"/>
       <c r="L394" s="20"/>
       <c r="M394" s="20"/>
@@ -53541,7 +54395,7 @@
       </c>
       <c r="S394" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T394" s="18">
         <f t="shared" si="154"/>
@@ -53586,70 +54440,100 @@
       </c>
       <c r="AE394" s="9">
         <f t="shared" si="148"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF394" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG394" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH394" s="64">
         <f t="shared" si="149"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI394" s="9">
         <f t="shared" si="150"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ394" s="5">
         <v>0.18</v>
       </c>
       <c r="AK394" s="11">
         <f t="shared" si="151"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL394" s="9">
         <f t="shared" si="152"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP394" s="12"/>
     </row>
     <row r="395" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A395" s="17"/>
-      <c r="C395" s="18"/>
-      <c r="E395" s="6"/>
-      <c r="F395" s="19"/>
-      <c r="G395" s="19"/>
-      <c r="H395" s="19"/>
-      <c r="I395" s="6"/>
+      <c r="A395" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B395" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C395" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D395" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E395" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F395" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G395" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H395" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I395" s="6" t="s">
+        <v>544</v>
+      </c>
       <c r="J395" s="6"/>
-      <c r="K395" s="18"/>
-      <c r="L395" s="18"/>
+      <c r="K395" s="18">
+        <v>40</v>
+      </c>
+      <c r="L395" s="18">
+        <v>40</v>
+      </c>
       <c r="M395" s="18"/>
       <c r="N395" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O395" s="18"/>
-      <c r="P395" s="18"/>
-      <c r="Q395" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O395" s="18">
+        <v>40</v>
+      </c>
+      <c r="P395" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q395" s="18">
+        <v>40</v>
+      </c>
       <c r="R395" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S395" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T395" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U395" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V395" s="18">
         <f t="shared" si="156"/>
@@ -53657,23 +54541,23 @@
       </c>
       <c r="W395" s="8">
         <f t="shared" ref="W395:W424" si="163">N395/10</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X395" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y395" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z395" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA395" s="8">
         <f t="shared" ref="AA395:AA424" si="164">R395/10</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB395" s="8">
         <v>39.270000000000003</v>
@@ -53686,14 +54570,14 @@
       </c>
       <c r="AE395" s="9">
         <f t="shared" ref="AE395:AE424" si="165">(J395*AB395)+(N395*AC395)+(AD395*S395)</f>
-        <v>0</v>
+        <v>18725</v>
       </c>
       <c r="AF395" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG395" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>2621.5000000000005</v>
       </c>
       <c r="AH395" s="64">
         <f t="shared" ref="AH395:AH424" si="166">(AB395*J395)*$AH$1</f>
@@ -53701,55 +54585,85 @@
       </c>
       <c r="AI395" s="9">
         <f t="shared" ref="AI395:AI424" si="167">AE395-AG395</f>
-        <v>0</v>
+        <v>16103.5</v>
       </c>
       <c r="AJ395" s="5">
         <v>0.18</v>
       </c>
       <c r="AK395" s="11">
         <f t="shared" ref="AK395:AK424" si="168">AI395*AJ395</f>
-        <v>0</v>
+        <v>2898.63</v>
       </c>
       <c r="AL395" s="9">
         <f t="shared" ref="AL395:AL424" si="169">AI395+AK395</f>
-        <v>0</v>
+        <v>19002.13</v>
       </c>
       <c r="AP395" s="12"/>
     </row>
     <row r="396" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A396" s="17"/>
-      <c r="C396" s="18"/>
-      <c r="E396" s="6"/>
-      <c r="F396" s="19"/>
-      <c r="G396" s="19"/>
-      <c r="H396" s="19"/>
-      <c r="I396" s="6"/>
+      <c r="A396" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B396" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C396" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D396" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E396" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F396" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G396" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H396" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I396" s="6" t="s">
+        <v>545</v>
+      </c>
       <c r="J396" s="55"/>
-      <c r="K396" s="18"/>
-      <c r="L396" s="18"/>
+      <c r="K396" s="18">
+        <v>80</v>
+      </c>
+      <c r="L396" s="18">
+        <v>80</v>
+      </c>
       <c r="M396" s="18"/>
       <c r="N396" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O396" s="18"/>
-      <c r="P396" s="18"/>
-      <c r="Q396" s="18"/>
+        <v>160</v>
+      </c>
+      <c r="O396" s="18">
+        <v>80</v>
+      </c>
+      <c r="P396" s="18">
+        <v>80</v>
+      </c>
+      <c r="Q396" s="18">
+        <v>80</v>
+      </c>
       <c r="R396" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S396" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T396" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U396" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V396" s="18">
         <f t="shared" si="156"/>
@@ -53757,23 +54671,23 @@
       </c>
       <c r="W396" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X396" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y396" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z396" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA396" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB396" s="8">
         <v>39.270000000000003</v>
@@ -53786,14 +54700,14 @@
       </c>
       <c r="AE396" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>37450</v>
       </c>
       <c r="AF396" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG396" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>5243.0000000000009</v>
       </c>
       <c r="AH396" s="64">
         <f t="shared" si="166"/>
@@ -53801,55 +54715,85 @@
       </c>
       <c r="AI396" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>32207</v>
       </c>
       <c r="AJ396" s="5">
         <v>0.18</v>
       </c>
       <c r="AK396" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>5797.26</v>
       </c>
       <c r="AL396" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>38004.26</v>
       </c>
       <c r="AP396" s="12"/>
     </row>
     <row r="397" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A397" s="17"/>
-      <c r="C397" s="18"/>
-      <c r="E397" s="6"/>
-      <c r="F397" s="19"/>
-      <c r="G397" s="19"/>
-      <c r="H397" s="19"/>
-      <c r="I397" s="6"/>
+      <c r="A397" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B397" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C397" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D397" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E397" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F397" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G397" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H397" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I397" s="6" t="s">
+        <v>405</v>
+      </c>
       <c r="J397" s="55"/>
-      <c r="K397" s="18"/>
-      <c r="L397" s="18"/>
+      <c r="K397" s="18">
+        <v>40</v>
+      </c>
+      <c r="L397" s="18">
+        <v>40</v>
+      </c>
       <c r="M397" s="18"/>
       <c r="N397" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O397" s="18"/>
-      <c r="P397" s="18"/>
-      <c r="Q397" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O397" s="18">
+        <v>40</v>
+      </c>
+      <c r="P397" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q397" s="18">
+        <v>40</v>
+      </c>
       <c r="R397" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S397" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T397" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U397" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V397" s="18">
         <f t="shared" si="156"/>
@@ -53857,23 +54801,23 @@
       </c>
       <c r="W397" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X397" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y397" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z397" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA397" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB397" s="8">
         <v>39.270000000000003</v>
@@ -53886,14 +54830,14 @@
       </c>
       <c r="AE397" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>18725</v>
       </c>
       <c r="AF397" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG397" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>2621.5000000000005</v>
       </c>
       <c r="AH397" s="64">
         <f t="shared" si="166"/>
@@ -53901,55 +54845,85 @@
       </c>
       <c r="AI397" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>16103.5</v>
       </c>
       <c r="AJ397" s="5">
         <v>0.18</v>
       </c>
       <c r="AK397" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>2898.63</v>
       </c>
       <c r="AL397" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>19002.13</v>
       </c>
       <c r="AP397" s="12"/>
     </row>
     <row r="398" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A398" s="17"/>
-      <c r="C398" s="18"/>
-      <c r="E398" s="6"/>
-      <c r="F398" s="19"/>
-      <c r="G398" s="19"/>
-      <c r="H398" s="19"/>
-      <c r="I398" s="6"/>
+      <c r="A398" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B398" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C398" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D398" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E398" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F398" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G398" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H398" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I398" s="6" t="s">
+        <v>546</v>
+      </c>
       <c r="J398" s="55"/>
-      <c r="K398" s="20"/>
-      <c r="L398" s="20"/>
+      <c r="K398" s="20">
+        <v>40</v>
+      </c>
+      <c r="L398" s="20">
+        <v>40</v>
+      </c>
       <c r="M398" s="20"/>
       <c r="N398" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O398" s="18"/>
-      <c r="P398" s="20"/>
-      <c r="Q398" s="20"/>
+        <v>80</v>
+      </c>
+      <c r="O398" s="18">
+        <v>40</v>
+      </c>
+      <c r="P398" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q398" s="20">
+        <v>40</v>
+      </c>
       <c r="R398" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S398" s="18">
         <f t="shared" si="153"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T398" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U398" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V398" s="18">
         <f t="shared" si="156"/>
@@ -53957,23 +54931,23 @@
       </c>
       <c r="W398" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X398" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y398" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z398" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA398" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB398" s="8">
         <v>39.270000000000003</v>
@@ -53986,14 +54960,14 @@
       </c>
       <c r="AE398" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>18725</v>
       </c>
       <c r="AF398" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG398" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>1217.125</v>
       </c>
       <c r="AH398" s="64">
         <f t="shared" si="166"/>
@@ -54001,52 +54975,82 @@
       </c>
       <c r="AI398" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>17507.875</v>
       </c>
       <c r="AJ398" s="5">
         <v>0.18</v>
       </c>
       <c r="AK398" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>3151.4175</v>
       </c>
       <c r="AL398" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>20659.2925</v>
       </c>
       <c r="AP398" s="12"/>
     </row>
     <row r="399" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A399" s="17"/>
-      <c r="C399" s="18"/>
-      <c r="E399" s="6"/>
-      <c r="F399" s="19"/>
-      <c r="G399" s="19"/>
-      <c r="H399" s="19"/>
-      <c r="I399" s="6"/>
+      <c r="A399" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B399" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C399" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D399" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E399" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F399" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G399" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H399" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I399" s="6" t="s">
+        <v>547</v>
+      </c>
       <c r="J399" s="55"/>
-      <c r="K399" s="18"/>
-      <c r="L399" s="20"/>
+      <c r="K399" s="18">
+        <v>40</v>
+      </c>
+      <c r="L399" s="20">
+        <v>40</v>
+      </c>
       <c r="M399" s="18"/>
       <c r="N399" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O399" s="18"/>
-      <c r="P399" s="20"/>
-      <c r="Q399" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O399" s="18">
+        <v>40</v>
+      </c>
+      <c r="P399" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q399" s="18">
+        <v>40</v>
+      </c>
       <c r="R399" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S399" s="18"/>
       <c r="T399" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U399" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V399" s="18">
         <f t="shared" si="156"/>
@@ -54054,23 +55058,23 @@
       </c>
       <c r="W399" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X399" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y399" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z399" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA399" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB399" s="8">
         <v>39.270000000000003</v>
@@ -54083,14 +55087,14 @@
       </c>
       <c r="AE399" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF399" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG399" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH399" s="64">
         <f t="shared" si="166"/>
@@ -54098,52 +55102,82 @@
       </c>
       <c r="AI399" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ399" s="5">
         <v>0.18</v>
       </c>
       <c r="AK399" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL399" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP399" s="12"/>
     </row>
     <row r="400" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A400" s="17"/>
-      <c r="C400" s="18"/>
-      <c r="E400" s="6"/>
-      <c r="F400" s="19"/>
-      <c r="G400" s="19"/>
-      <c r="H400" s="19"/>
-      <c r="I400" s="6"/>
+      <c r="A400" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B400" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C400" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D400" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E400" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F400" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G400" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H400" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I400" s="6" t="s">
+        <v>548</v>
+      </c>
       <c r="J400" s="55"/>
-      <c r="K400" s="20"/>
-      <c r="L400" s="20"/>
+      <c r="K400" s="20">
+        <v>40</v>
+      </c>
+      <c r="L400" s="20">
+        <v>40</v>
+      </c>
       <c r="M400" s="20"/>
       <c r="N400" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O400" s="18"/>
-      <c r="P400" s="18"/>
-      <c r="Q400" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O400" s="18">
+        <v>40</v>
+      </c>
+      <c r="P400" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q400" s="18">
+        <v>40</v>
+      </c>
       <c r="R400" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S400" s="18"/>
       <c r="T400" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U400" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V400" s="18">
         <f t="shared" si="156"/>
@@ -54151,23 +55185,23 @@
       </c>
       <c r="W400" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X400" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y400" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z400" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA400" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB400" s="8">
         <v>39.270000000000003</v>
@@ -54180,14 +55214,14 @@
       </c>
       <c r="AE400" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF400" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG400" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH400" s="64">
         <f t="shared" si="166"/>
@@ -54195,52 +55229,82 @@
       </c>
       <c r="AI400" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ400" s="5">
         <v>0.18</v>
       </c>
       <c r="AK400" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL400" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP400" s="12"/>
     </row>
     <row r="401" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A401" s="17"/>
-      <c r="C401" s="18"/>
-      <c r="E401" s="6"/>
-      <c r="F401" s="19"/>
-      <c r="G401" s="19"/>
-      <c r="H401" s="19"/>
-      <c r="I401" s="6"/>
+      <c r="A401" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B401" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C401" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D401" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E401" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F401" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G401" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H401" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I401" s="6" t="s">
+        <v>549</v>
+      </c>
       <c r="J401" s="55"/>
-      <c r="K401" s="20"/>
-      <c r="L401" s="20"/>
+      <c r="K401" s="20">
+        <v>40</v>
+      </c>
+      <c r="L401" s="20">
+        <v>40</v>
+      </c>
       <c r="M401" s="20"/>
       <c r="N401" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O401" s="18"/>
-      <c r="P401" s="18"/>
-      <c r="Q401" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O401" s="18">
+        <v>40</v>
+      </c>
+      <c r="P401" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q401" s="18">
+        <v>40</v>
+      </c>
       <c r="R401" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S401" s="18"/>
       <c r="T401" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U401" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V401" s="18">
         <f t="shared" si="156"/>
@@ -54248,23 +55312,23 @@
       </c>
       <c r="W401" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X401" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y401" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z401" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA401" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB401" s="8">
         <v>39.270000000000003</v>
@@ -54277,14 +55341,14 @@
       </c>
       <c r="AE401" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF401" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG401" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH401" s="64">
         <f t="shared" si="166"/>
@@ -54292,52 +55356,82 @@
       </c>
       <c r="AI401" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ401" s="5">
         <v>0.18</v>
       </c>
       <c r="AK401" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL401" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP401" s="12"/>
     </row>
     <row r="402" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A402" s="17"/>
-      <c r="C402" s="18"/>
-      <c r="E402" s="6"/>
-      <c r="F402" s="19"/>
-      <c r="G402" s="19"/>
-      <c r="H402" s="19"/>
-      <c r="I402" s="6"/>
+      <c r="A402" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B402" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C402" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D402" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E402" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F402" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G402" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H402" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I402" s="6" t="s">
+        <v>550</v>
+      </c>
       <c r="J402" s="55"/>
-      <c r="K402" s="20"/>
-      <c r="L402" s="20"/>
+      <c r="K402" s="20">
+        <v>40</v>
+      </c>
+      <c r="L402" s="20">
+        <v>40</v>
+      </c>
       <c r="M402" s="20"/>
       <c r="N402" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O402" s="18"/>
-      <c r="P402" s="18"/>
-      <c r="Q402" s="20"/>
+        <v>80</v>
+      </c>
+      <c r="O402" s="18">
+        <v>40</v>
+      </c>
+      <c r="P402" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q402" s="20">
+        <v>40</v>
+      </c>
       <c r="R402" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S402" s="18"/>
       <c r="T402" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U402" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V402" s="18">
         <f t="shared" si="156"/>
@@ -54345,23 +55439,23 @@
       </c>
       <c r="W402" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X402" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y402" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z402" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA402" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB402" s="8">
         <v>39.270000000000003</v>
@@ -54374,14 +55468,14 @@
       </c>
       <c r="AE402" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF402" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG402" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH402" s="64">
         <f t="shared" si="166"/>
@@ -54389,52 +55483,82 @@
       </c>
       <c r="AI402" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ402" s="5">
         <v>0.18</v>
       </c>
       <c r="AK402" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL402" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP402" s="12"/>
     </row>
     <row r="403" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A403" s="17"/>
-      <c r="C403" s="18"/>
-      <c r="E403" s="6"/>
-      <c r="F403" s="19"/>
-      <c r="G403" s="19"/>
-      <c r="H403" s="19"/>
-      <c r="I403" s="6"/>
+      <c r="A403" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B403" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C403" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D403" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E403" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F403" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G403" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H403" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I403" s="6" t="s">
+        <v>551</v>
+      </c>
       <c r="J403" s="55"/>
-      <c r="K403" s="20"/>
-      <c r="L403" s="20"/>
+      <c r="K403" s="20">
+        <v>80</v>
+      </c>
+      <c r="L403" s="20">
+        <v>80</v>
+      </c>
       <c r="M403" s="20"/>
       <c r="N403" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O403" s="18"/>
-      <c r="P403" s="18"/>
-      <c r="Q403" s="18"/>
+        <v>160</v>
+      </c>
+      <c r="O403" s="18">
+        <v>80</v>
+      </c>
+      <c r="P403" s="18">
+        <v>80</v>
+      </c>
+      <c r="Q403" s="18">
+        <v>80</v>
+      </c>
       <c r="R403" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S403" s="18"/>
       <c r="T403" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U403" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V403" s="18">
         <f t="shared" si="156"/>
@@ -54442,23 +55566,23 @@
       </c>
       <c r="W403" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X403" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y403" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z403" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA403" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB403" s="8">
         <v>39.270000000000003</v>
@@ -54471,14 +55595,14 @@
       </c>
       <c r="AE403" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>8394</v>
       </c>
       <c r="AF403" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG403" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>545.61</v>
       </c>
       <c r="AH403" s="64">
         <f t="shared" si="166"/>
@@ -54486,52 +55610,82 @@
       </c>
       <c r="AI403" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>7848.39</v>
       </c>
       <c r="AJ403" s="5">
         <v>0.18</v>
       </c>
       <c r="AK403" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>1412.7102</v>
       </c>
       <c r="AL403" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>9261.1002000000008</v>
       </c>
       <c r="AP403" s="12"/>
     </row>
     <row r="404" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A404" s="17"/>
-      <c r="C404" s="18"/>
-      <c r="E404" s="6"/>
-      <c r="F404" s="19"/>
-      <c r="G404" s="19"/>
-      <c r="H404" s="19"/>
-      <c r="I404" s="6"/>
+      <c r="A404" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B404" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C404" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D404" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E404" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F404" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G404" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H404" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I404" s="6" t="s">
+        <v>552</v>
+      </c>
       <c r="J404" s="55"/>
-      <c r="K404" s="20"/>
-      <c r="L404" s="20"/>
+      <c r="K404" s="20">
+        <v>40</v>
+      </c>
+      <c r="L404" s="20">
+        <v>40</v>
+      </c>
       <c r="M404" s="20"/>
       <c r="N404" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O404" s="18"/>
-      <c r="P404" s="20"/>
-      <c r="Q404" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O404" s="18">
+        <v>40</v>
+      </c>
+      <c r="P404" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q404" s="18">
+        <v>40</v>
+      </c>
       <c r="R404" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S404" s="18"/>
       <c r="T404" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U404" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V404" s="18">
         <f t="shared" si="156"/>
@@ -54539,23 +55693,23 @@
       </c>
       <c r="W404" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X404" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y404" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z404" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA404" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB404" s="8">
         <v>39.270000000000003</v>
@@ -54568,14 +55722,14 @@
       </c>
       <c r="AE404" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF404" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG404" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>272.80500000000001</v>
       </c>
       <c r="AH404" s="64">
         <f t="shared" si="166"/>
@@ -54583,52 +55737,82 @@
       </c>
       <c r="AI404" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>3924.1950000000002</v>
       </c>
       <c r="AJ404" s="5">
         <v>0.18</v>
       </c>
       <c r="AK404" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>706.35509999999999</v>
       </c>
       <c r="AL404" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>4630.5501000000004</v>
       </c>
       <c r="AP404" s="12"/>
     </row>
     <row r="405" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A405" s="17"/>
-      <c r="C405" s="18"/>
-      <c r="E405" s="6"/>
-      <c r="F405" s="19"/>
-      <c r="G405" s="19"/>
-      <c r="H405" s="19"/>
-      <c r="I405" s="6"/>
+      <c r="A405" s="71">
+        <v>46203</v>
+      </c>
+      <c r="B405" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C405" s="74">
+        <v>1176.7759999954201</v>
+      </c>
+      <c r="D405" s="74">
+        <v>40948.753804686399</v>
+      </c>
+      <c r="E405" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F405" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G405" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H405" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I405" s="6" t="s">
+        <v>553</v>
+      </c>
       <c r="J405" s="55"/>
-      <c r="K405" s="20"/>
-      <c r="L405" s="20"/>
+      <c r="K405" s="20">
+        <v>40</v>
+      </c>
+      <c r="L405" s="20">
+        <v>40</v>
+      </c>
       <c r="M405" s="20"/>
       <c r="N405" s="8">
         <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
-      <c r="O405" s="18"/>
-      <c r="P405" s="18"/>
-      <c r="Q405" s="18"/>
+        <v>80</v>
+      </c>
+      <c r="O405" s="18">
+        <v>40</v>
+      </c>
+      <c r="P405" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q405" s="18">
+        <v>40</v>
+      </c>
       <c r="R405" s="8">
         <f t="shared" si="161"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S405" s="18"/>
       <c r="T405" s="18">
         <f t="shared" si="154"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U405" s="18">
         <f t="shared" si="155"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V405" s="18">
         <f t="shared" si="156"/>
@@ -54636,23 +55820,23 @@
       </c>
       <c r="W405" s="8">
         <f t="shared" si="163"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X405" s="18">
         <f t="shared" si="157"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y405" s="18">
         <f t="shared" si="158"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z405" s="18">
         <f t="shared" si="159"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA405" s="8">
         <f t="shared" si="164"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB405" s="8">
         <v>39.270000000000003</v>
@@ -54665,14 +55849,14 @@
       </c>
       <c r="AE405" s="9">
         <f t="shared" si="165"/>
-        <v>0</v>
+        <v>4197</v>
       </c>
       <c r="AF405" s="21">
         <v>0.1</v>
       </c>
       <c r="AG405" s="10">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>419.70000000000005</v>
       </c>
       <c r="AH405" s="64">
         <f t="shared" si="166"/>
@@ -54680,18 +55864,18 @@
       </c>
       <c r="AI405" s="9">
         <f t="shared" si="167"/>
-        <v>0</v>
+        <v>3777.3</v>
       </c>
       <c r="AJ405" s="5">
         <v>0.18</v>
       </c>
       <c r="AK405" s="11">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>679.91399999999999</v>
       </c>
       <c r="AL405" s="9">
         <f t="shared" si="169"/>
-        <v>0</v>
+        <v>4457.2139999999999</v>
       </c>
       <c r="AP405" s="12"/>
     </row>
@@ -56548,15 +57732,15 @@
       <c r="I425" s="6"/>
       <c r="J425" s="6">
         <f t="shared" ref="J425:AA425" si="177">SUM(J3:J424)</f>
-        <v>6591</v>
+        <v>7003</v>
       </c>
       <c r="K425" s="6">
         <f t="shared" si="177"/>
-        <v>16998</v>
+        <v>17679</v>
       </c>
       <c r="L425" s="6">
         <f t="shared" si="177"/>
-        <v>16242</v>
+        <v>16923</v>
       </c>
       <c r="M425" s="6">
         <f t="shared" si="177"/>
@@ -56564,23 +57748,23 @@
       </c>
       <c r="N425" s="6">
         <f t="shared" si="177"/>
-        <v>50763</v>
+        <v>52125</v>
       </c>
       <c r="O425" s="6">
         <f t="shared" si="177"/>
-        <v>24456</v>
+        <v>25222</v>
       </c>
       <c r="P425" s="6">
         <f t="shared" si="177"/>
-        <v>20995</v>
+        <v>21651</v>
       </c>
       <c r="Q425" s="6">
         <f t="shared" si="177"/>
-        <v>29259</v>
+        <v>30027</v>
       </c>
       <c r="R425" s="6">
         <f>SUM(R3:R424)</f>
-        <v>74710</v>
+        <v>76900</v>
       </c>
       <c r="S425" s="6" t="e">
         <f>SUM(S3:S424)</f>
@@ -56588,11 +57772,11 @@
       </c>
       <c r="T425" s="6">
         <f t="shared" si="177"/>
-        <v>1699.4</v>
+        <v>1767.5</v>
       </c>
       <c r="U425" s="6">
         <f t="shared" si="177"/>
-        <v>1623.9000000000003</v>
+        <v>1692.0000000000002</v>
       </c>
       <c r="V425" s="6">
         <f t="shared" si="177"/>
@@ -56600,23 +57784,23 @@
       </c>
       <c r="W425" s="6">
         <f t="shared" si="177"/>
-        <v>5075.45</v>
+        <v>5211.6499999999996</v>
       </c>
       <c r="X425" s="6">
         <f t="shared" si="177"/>
-        <v>2445.6000000000004</v>
+        <v>2522.2000000000003</v>
       </c>
       <c r="Y425" s="6">
         <f t="shared" si="177"/>
-        <v>2099.5</v>
+        <v>2165.1</v>
       </c>
       <c r="Z425" s="6">
         <f t="shared" si="177"/>
-        <v>2925.9</v>
+        <v>3002.7000000000003</v>
       </c>
       <c r="AA425" s="6">
         <f t="shared" si="177"/>
-        <v>7470.9999999999991</v>
+        <v>7689.9999999999991</v>
       </c>
       <c r="AB425" s="6"/>
       <c r="AC425" s="6"/>
@@ -56721,15 +57905,15 @@
       </c>
       <c r="J429" s="61">
         <f t="shared" ref="J429:AF429" si="178">+J425/40</f>
-        <v>164.77500000000001</v>
+        <v>175.07499999999999</v>
       </c>
       <c r="K429" s="62">
         <f t="shared" si="178"/>
-        <v>424.95</v>
+        <v>441.97500000000002</v>
       </c>
       <c r="L429" s="62">
         <f t="shared" si="178"/>
-        <v>406.05</v>
+        <v>423.07499999999999</v>
       </c>
       <c r="M429" s="62">
         <f t="shared" si="178"/>
@@ -56737,23 +57921,23 @@
       </c>
       <c r="N429" s="61">
         <f t="shared" si="178"/>
-        <v>1269.075</v>
+        <v>1303.125</v>
       </c>
       <c r="O429" s="62">
         <f t="shared" si="178"/>
-        <v>611.4</v>
+        <v>630.54999999999995</v>
       </c>
       <c r="P429" s="62">
         <f t="shared" si="178"/>
-        <v>524.875</v>
+        <v>541.27499999999998</v>
       </c>
       <c r="Q429" s="62">
         <f t="shared" si="178"/>
-        <v>731.47500000000002</v>
+        <v>750.67499999999995</v>
       </c>
       <c r="R429" s="61">
         <f t="shared" si="178"/>
-        <v>1867.75</v>
+        <v>1922.5</v>
       </c>
       <c r="S429" s="80" t="e">
         <f t="shared" si="178"/>
@@ -56761,11 +57945,11 @@
       </c>
       <c r="T429" s="80">
         <f t="shared" si="178"/>
-        <v>42.484999999999999</v>
+        <v>44.1875</v>
       </c>
       <c r="U429" s="80">
         <f t="shared" si="178"/>
-        <v>40.597500000000011</v>
+        <v>42.300000000000004</v>
       </c>
       <c r="V429" s="80">
         <f t="shared" si="178"/>
@@ -56773,23 +57957,23 @@
       </c>
       <c r="W429" s="80">
         <f t="shared" si="178"/>
-        <v>126.88624999999999</v>
+        <v>130.29124999999999</v>
       </c>
       <c r="X429" s="80">
         <f t="shared" si="178"/>
-        <v>61.140000000000008</v>
+        <v>63.055000000000007</v>
       </c>
       <c r="Y429" s="80">
         <f t="shared" si="178"/>
-        <v>52.487499999999997</v>
+        <v>54.127499999999998</v>
       </c>
       <c r="Z429" s="80">
         <f t="shared" si="178"/>
-        <v>73.147500000000008</v>
+        <v>75.06750000000001</v>
       </c>
       <c r="AA429" s="80">
         <f t="shared" si="178"/>
-        <v>186.77499999999998</v>
+        <v>192.24999999999997</v>
       </c>
       <c r="AB429" s="81"/>
       <c r="AC429" s="57">
@@ -56844,13 +58028,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -56863,14 +58048,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -56942,11 +58126,11 @@
       </c>
       <c r="G7" s="29">
         <f>'STT Report'!Q429+'STT Report'!Z429</f>
-        <v>804.62250000000006</v>
+        <v>825.74249999999995</v>
       </c>
       <c r="H7" s="30">
         <f>E7+F7-G7</f>
-        <v>124.47749999999996</v>
+        <v>103.35750000000007</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -56961,11 +58145,11 @@
       </c>
       <c r="G8" s="29">
         <f>'STT Report'!P429+'STT Report'!Y429</f>
-        <v>577.36249999999995</v>
+        <v>595.40249999999992</v>
       </c>
       <c r="H8" s="30">
         <f>E8+F8-G8</f>
-        <v>101.73750000000007</v>
+        <v>83.697500000000105</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -56980,11 +58164,11 @@
       </c>
       <c r="G9" s="29">
         <f>'STT Report'!O429+'STT Report'!X429</f>
-        <v>672.54</v>
+        <v>693.60500000000002</v>
       </c>
       <c r="H9" s="30">
         <f>E9+F9-G9</f>
-        <v>195.76</v>
+        <v>174.69499999999994</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -57001,11 +58185,11 @@
       </c>
       <c r="G10" s="35">
         <f>SUM(G7:G9)</f>
-        <v>2054.5250000000001</v>
+        <v>2114.75</v>
       </c>
       <c r="H10" s="36">
         <f>SUM(H7:H9)</f>
-        <v>421.97500000000002</v>
+        <v>361.75000000000011</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -57020,11 +58204,11 @@
       </c>
       <c r="G11" s="58">
         <f>'STT Report'!J429</f>
-        <v>164.77500000000001</v>
+        <v>175.07499999999999</v>
       </c>
       <c r="H11" s="30">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>1710.125</v>
+        <v>1699.825</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -57061,11 +58245,11 @@
       </c>
       <c r="G14" s="33">
         <f>SUM(G11:G13)</f>
-        <v>164.77500000000001</v>
+        <v>175.07499999999999</v>
       </c>
       <c r="H14" s="36">
         <f>SUM(H11:H13)</f>
-        <v>1710.125</v>
+        <v>1699.825</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -57099,11 +58283,11 @@
       </c>
       <c r="G16" s="29">
         <f>'STT Report'!L429+'STT Report'!U429</f>
-        <v>446.64750000000004</v>
+        <v>465.375</v>
       </c>
       <c r="H16" s="30">
         <f>E16+F16-G16</f>
-        <v>187.35249999999996</v>
+        <v>168.625</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -57118,11 +58302,11 @@
       </c>
       <c r="G17" s="29">
         <f>'STT Report'!K429+'STT Report'!T429</f>
-        <v>467.435</v>
+        <v>486.16250000000002</v>
       </c>
       <c r="H17" s="30">
         <f>E17+F17-G17</f>
-        <v>161.26500000000004</v>
+        <v>142.53750000000002</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -57139,11 +58323,11 @@
       </c>
       <c r="G18" s="35">
         <f>SUM(G15:G17)</f>
-        <v>1395.9612500000001</v>
+        <v>1433.41625</v>
       </c>
       <c r="H18" s="36">
         <f>SUM(H15:H17)</f>
-        <v>251.83875000000006</v>
+        <v>214.38375000000008</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -57160,11 +58344,11 @@
       </c>
       <c r="G19" s="38">
         <f>G10+G14+G18</f>
-        <v>3615.2612500000005</v>
+        <v>3723.24125</v>
       </c>
       <c r="H19" s="40">
         <f>H10+H14+H18</f>
-        <v>2383.9387499999998</v>
+        <v>2275.9587500000002</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
